--- a/jira_export_2026-07-02.xlsx
+++ b/jira_export_2026-07-02.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>1,298 €</t>
+          <t>2,326 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -760,7 +760,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>219 €</t>
+          <t>1,248 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>38 h</t>
+          <t>52 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -886,7 +886,7 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B25" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>254</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P91"/>
+  <dimension ref="A1:P98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1414,32 +1414,32 @@
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-33841</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
+          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>Commune de Nans les Pins</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Modélisation Seyne S/ Mer</t>
+          <t>MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -1449,49 +1449,49 @@
       </c>
       <c r="H10" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J10" s="14" t="n">
         <v>1</v>
       </c>
       <c r="K10" s="14" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="L10" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33850</t>
         </is>
       </c>
       <c r="M10" s="14" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00161103</t>
         </is>
       </c>
       <c r="N10" s="15" t="n">
-        <v>657.3</v>
-      </c>
-      <c r="O10" s="16" t="n">
-        <v>219.1</v>
+        <v>0</v>
+      </c>
+      <c r="O10" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="P10" s="15" t="n">
-        <v>175.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>[CD 73)] - Purge arrêtés temporaires</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Purge arrêtés temporaires</t>
+          <t>Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
@@ -1533,57 +1533,57 @@
         <v>1</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="N11" s="12" t="n">
-        <v>1890</v>
+        <v>657.3</v>
       </c>
       <c r="O11" s="16" t="n">
-        <v>0</v>
+        <v>219.1</v>
       </c>
       <c r="P11" s="12" t="n">
-        <v>0</v>
+        <v>175.28</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33755</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MAINTENON] - Migration vers GeoDP V2</t>
+          <t>[CD 73)] - Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Quentin BORDILLON</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MAINTENON</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -1593,12 +1593,12 @@
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I12" s="14" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J12" s="14" t="n">
@@ -1609,16 +1609,16 @@
       </c>
       <c r="L12" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33764</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="M12" s="14" t="inlineStr">
         <is>
-          <t>00169558</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="N12" s="15" t="n">
-        <v>1365</v>
+        <v>1890</v>
       </c>
       <c r="O12" s="16" t="n">
         <v>0</v>
@@ -1630,27 +1630,27 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33720</t>
+          <t>PDMDEP-33790</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LEVALLOIS PERRET] - PRESTA PURGE DES ACTES EN URGENCE</t>
+          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>PRESTA PURGE DES ACTES EN URGENCE</t>
+          <t xml:space="preserve">Commande modélisation supplémentaire </t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
@@ -1670,29 +1670,29 @@
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="J13" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33724</t>
+          <t>PDMDEP-33794</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
-          <t>00169462</t>
+          <t>00169697</t>
         </is>
       </c>
       <c r="N13" s="12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="O13" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P13" s="12" t="n">
@@ -1702,27 +1702,27 @@
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33686</t>
+          <t>PDMDEP-33755</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>[EUROMETROPOLE DE METZ] - Paiement CB + 3 PAX</t>
+          <t>[COMMUNE DE MAINTENON] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Quentin BORDILLON</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>EUROMETROPOLE DE METZ</t>
+          <t>COMMUNE DE MAINTENON</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>Paiement CB + 3 PAX</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
@@ -1737,12 +1737,12 @@
       </c>
       <c r="H14" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J14" s="14" t="n">
@@ -1753,16 +1753,16 @@
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33694</t>
+          <t>PDMDEP-33764</t>
         </is>
       </c>
       <c r="M14" s="14" t="inlineStr">
         <is>
-          <t>00169321</t>
+          <t>00169558</t>
         </is>
       </c>
       <c r="N14" s="15" t="n">
-        <v>1500</v>
+        <v>1365</v>
       </c>
       <c r="O14" s="16" t="n">
         <v>0</v>
@@ -1774,32 +1774,32 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33610</t>
+          <t>PDMDEP-33720</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MORLAIX] - MIGRATION GEODP PLACIER hors matériel </t>
+          <t>[COMMUNE DE LEVALLOIS PERRET] - PRESTA PURGE DES ACTES EN URGENCE</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Quentin BORDILLON</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MORLAIX</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
+          <t>PRESTA PURGE DES ACTES EN URGENCE</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr">
@@ -1809,32 +1809,32 @@
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J15" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33616</t>
+          <t>PDMDEP-33724</t>
         </is>
       </c>
       <c r="M15" s="11" t="inlineStr">
         <is>
-          <t>00169015</t>
+          <t>00169462</t>
         </is>
       </c>
       <c r="N15" s="12" t="n">
-        <v>4040</v>
+        <v>1000</v>
       </c>
       <c r="O15" s="16" t="n">
         <v>0</v>
@@ -1846,32 +1846,32 @@
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33566</t>
+          <t>PDMDEP-33686</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LILLE] Flux WFS</t>
+          <t>[EUROMETROPOLE DE METZ] - Paiement CB + 3 PAX</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LILLE</t>
+          <t>EUROMETROPOLE DE METZ</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>MM - Up - LiExp - Flux WFS (PS)</t>
+          <t>Paiement CB + 3 PAX</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I16" s="14" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="J16" s="14" t="n">
@@ -1897,16 +1897,16 @@
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33570</t>
+          <t>PDMDEP-33694</t>
         </is>
       </c>
       <c r="M16" s="14" t="inlineStr">
         <is>
-          <t>00168466</t>
+          <t>00169321</t>
         </is>
       </c>
       <c r="N16" s="15" t="n">
-        <v>895</v>
+        <v>1500</v>
       </c>
       <c r="O16" s="16" t="n">
         <v>0</v>
@@ -1918,27 +1918,27 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33553</t>
+          <t>PDMDEP-33610</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - MM - Up - GeODP - PAX</t>
+          <t xml:space="preserve">[COMMUNE DE MORLAIX] - MIGRATION GEODP PLACIER hors matériel </t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Quentin BORDILLON</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>COMMUNE DE MORLAIX</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>MM - Up - GeODP - PAX</t>
+          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J17" s="11" t="n">
@@ -1969,16 +1969,16 @@
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33561</t>
+          <t>PDMDEP-33616</t>
         </is>
       </c>
       <c r="M17" s="11" t="inlineStr">
         <is>
-          <t>00168460</t>
+          <t>00169015</t>
         </is>
       </c>
       <c r="N17" s="12" t="n">
-        <v>500</v>
+        <v>4040</v>
       </c>
       <c r="O17" s="16" t="n">
         <v>0</v>
@@ -1990,12 +1990,12 @@
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33566</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t>[COMMUNE DE LILLE] Flux WFS</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
@@ -2005,12 +2005,12 @@
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t>COMMUNE DE LILLE</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t>MM - Up - LiExp - Flux WFS (PS)</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
@@ -2030,27 +2030,27 @@
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="J18" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K18" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33570</t>
         </is>
       </c>
       <c r="M18" s="14" t="inlineStr">
         <is>
-          <t>00168025</t>
+          <t>00168466</t>
         </is>
       </c>
       <c r="N18" s="15" t="n">
-        <v>171.4</v>
+        <v>895</v>
       </c>
       <c r="O18" s="16" t="n">
         <v>0</v>
@@ -2062,27 +2062,27 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33461</t>
+          <t>PDMDEP-33553</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>[Mairie de Buis-les-baronnies] - INITIATION GEODP</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - MM - Up - GeODP - PAX</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Mairie de Buis-les-baronnies</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>INITIATION GEODP</t>
+          <t>MM - Up - GeODP - PAX</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
@@ -2102,27 +2102,27 @@
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="J19" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K19" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33465</t>
+          <t>PDMDEP-33561</t>
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr">
         <is>
-          <t>00167986</t>
+          <t>00168460</t>
         </is>
       </c>
       <c r="N19" s="12" t="n">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="O19" s="16" t="n">
         <v>0</v>
@@ -2134,12 +2134,12 @@
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33386</t>
+          <t>PDMDEP-33471</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE SAINT PIERRE DE LA REUNION] - Prestation modélisation Littéralis </t>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SAINT PIERRE DE LA REUNION</t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prestation modélisation Littéralis </t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
@@ -2174,27 +2174,27 @@
       </c>
       <c r="I20" s="14" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J20" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K20" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33390</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="M20" s="14" t="inlineStr">
         <is>
-          <t>00167823</t>
+          <t>00168025</t>
         </is>
       </c>
       <c r="N20" s="15" t="n">
-        <v>205.68</v>
+        <v>171.4</v>
       </c>
       <c r="O20" s="16" t="n">
         <v>0</v>
@@ -2206,37 +2206,37 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33363</t>
+          <t>PDMDEP-33461</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>[AMIENS METROPOLE] LiExp - Vérif</t>
+          <t>[Mairie de Buis-les-baronnies] - INITIATION GEODP</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>AMIENS METROPOLE</t>
+          <t>Mairie de Buis-les-baronnies</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>MM - Up - LiExp - Vérif</t>
+          <t>INITIATION GEODP</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H21" s="11" t="inlineStr">
@@ -2246,21 +2246,29 @@
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J21" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L21" s="11" t="inlineStr"/>
-      <c r="M21" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L21" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-33465</t>
+        </is>
+      </c>
+      <c r="M21" s="11" t="inlineStr">
+        <is>
+          <t>00167986</t>
+        </is>
+      </c>
       <c r="N21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="12" t="n">
+        <v>450</v>
+      </c>
+      <c r="O21" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P21" s="12" t="n">
@@ -2270,12 +2278,12 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33348</t>
+          <t>PDMDEP-33386</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[MAISONS ALFORT] - Modélisation + Modif Marianne </t>
+          <t xml:space="preserve">[COMMUNE DE SAINT PIERRE DE LA REUNION] - Prestation modélisation Littéralis </t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
@@ -2285,12 +2293,12 @@
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMUNE DE MAISONS ALFORT </t>
+          <t>COMMUNE DE SAINT PIERRE DE LA REUNION</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modélisation + Modif Marianne </t>
+          <t xml:space="preserve">Prestation modélisation Littéralis </t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
@@ -2310,59 +2318,59 @@
       </c>
       <c r="I22" s="14" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J22" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K22" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33352</t>
+          <t>PDMDEP-33390</t>
         </is>
       </c>
       <c r="M22" s="14" t="inlineStr">
         <is>
-          <t>00167402</t>
+          <t>00167823</t>
         </is>
       </c>
       <c r="N22" s="15" t="n">
-        <v>171.4</v>
-      </c>
-      <c r="O22" s="16" t="n">
-        <v>0</v>
+        <v>617.04</v>
+      </c>
+      <c r="O22" s="15" t="n">
+        <v>1028.4</v>
       </c>
       <c r="P22" s="15" t="n">
-        <v>0</v>
+        <v>4113.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33363</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - Crédits 21 heures (3j)</t>
+          <t>[AMIENS METROPOLE] LiExp - Vérif</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>AMIENS METROPOLE</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>MM - Up - LiExp - Vérif</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
@@ -2372,7 +2380,7 @@
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
@@ -2382,29 +2390,21 @@
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="J23" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L23" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-33232</t>
-        </is>
-      </c>
-      <c r="M23" s="11" t="inlineStr">
-        <is>
-          <t>00166708</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L23" s="11" t="inlineStr"/>
+      <c r="M23" s="11" t="inlineStr"/>
       <c r="N23" s="12" t="n">
-        <v>1250</v>
-      </c>
-      <c r="O23" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P23" s="12" t="n">
@@ -2414,27 +2414,27 @@
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33348</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - Crédits 21 heures (3j)</t>
+          <t xml:space="preserve">[MAISONS ALFORT] - Modélisation + Modif Marianne </t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t xml:space="preserve">COMMUNE DE MAISONS ALFORT </t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t xml:space="preserve">Modélisation + Modif Marianne </t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
@@ -2454,27 +2454,27 @@
       </c>
       <c r="I24" s="14" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="J24" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K24" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33231</t>
+          <t>PDMDEP-33352</t>
         </is>
       </c>
       <c r="M24" s="14" t="inlineStr">
         <is>
-          <t>00166707</t>
+          <t>00167402</t>
         </is>
       </c>
       <c r="N24" s="15" t="n">
-        <v>600</v>
+        <v>171.4</v>
       </c>
       <c r="O24" s="16" t="n">
         <v>0</v>
@@ -2486,27 +2486,27 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33203</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>[CD 38] - LiExp - Crédits d'heure + TDC MV</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - Crédits 21 heures (3j)</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>LiExp - Crédits d'heure + TDC MV</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
@@ -2526,27 +2526,27 @@
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J25" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33207</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>00166553</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N25" s="12" t="n">
-        <v>184.5</v>
+        <v>1250</v>
       </c>
       <c r="O25" s="16" t="n">
         <v>0</v>
@@ -2558,32 +2558,32 @@
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33012</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - Crédits 21 heures (3j)</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE GRASSE</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP + Module Terrasse + formation sur site</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G26" s="14" t="inlineStr">
@@ -2593,69 +2593,69 @@
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J26" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K26" s="14" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33021</t>
+          <t>PDMDEP-33231</t>
         </is>
       </c>
       <c r="M26" s="14" t="inlineStr">
         <is>
-          <t>00165368</t>
+          <t>00166707</t>
         </is>
       </c>
       <c r="N26" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="15" t="n">
-        <v>1079</v>
+        <v>600</v>
+      </c>
+      <c r="O26" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P26" s="15" t="n">
-        <v>2158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33012</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE GRASSE</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
@@ -2665,69 +2665,69 @@
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="J27" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33021</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00165368</t>
         </is>
       </c>
       <c r="N27" s="12" t="n">
-        <v>2000</v>
-      </c>
-      <c r="O27" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O27" s="12" t="n">
+        <v>1079</v>
       </c>
       <c r="P27" s="12" t="n">
-        <v>0</v>
+        <v>719.33</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32848</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GRENOBLE] - Modification modèles de facture</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE GRENOBLE</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>Modification modèles de facture</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G28" s="14" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="I28" s="14" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J28" s="14" t="n">
@@ -2753,16 +2753,16 @@
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32852</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M28" s="14" t="inlineStr">
         <is>
-          <t>00164564</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N28" s="15" t="n">
-        <v>300</v>
+        <v>2000</v>
       </c>
       <c r="O28" s="16" t="n">
         <v>0</v>
@@ -2774,12 +2774,12 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32831</t>
+          <t>PDMDEP-32848</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE PANTIN] - Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
+          <t>[COMMUNE DE GRENOBLE] - Modification modèles de facture</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
@@ -2789,12 +2789,12 @@
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE PANTIN</t>
+          <t>COMMUNE DE GRENOBLE</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
+          <t>Modification modèles de facture</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="J29" s="11" t="n">
@@ -2825,16 +2825,16 @@
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32837</t>
+          <t>PDMDEP-32852</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>00164275</t>
+          <t>00164564</t>
         </is>
       </c>
       <c r="N29" s="12" t="n">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="O29" s="16" t="n">
         <v>0</v>
@@ -2846,32 +2846,32 @@
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32768</t>
+          <t>PDMDEP-32831</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
+          <t>[COMMUNE DE PANTIN] - Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE REIMS</t>
+          <t>COMMUNE DE PANTIN</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>MV app/ infra + màj carto</t>
+          <t>Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G30" s="14" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="I30" s="14" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="J30" s="14" t="n">
@@ -2897,16 +2897,16 @@
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32772</t>
+          <t>PDMDEP-32837</t>
         </is>
       </c>
       <c r="M30" s="14" t="inlineStr">
         <is>
-          <t>00163806</t>
+          <t>00164275</t>
         </is>
       </c>
       <c r="N30" s="15" t="n">
-        <v>705</v>
+        <v>900</v>
       </c>
       <c r="O30" s="16" t="n">
         <v>0</v>
@@ -2918,12 +2918,12 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32759</t>
+          <t>PDMDEP-32768</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE DU GRAND REIMS - DSIT] - MV app/ infra + màj carto</t>
+          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE DU GRAND REIMS - DSIT</t>
+          <t>VILLE DE REIMS</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
@@ -2969,16 +2969,16 @@
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32763</t>
+          <t>PDMDEP-32772</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>00163805</t>
+          <t>00163806</t>
         </is>
       </c>
       <c r="N31" s="12" t="n">
-        <v>564</v>
+        <v>705</v>
       </c>
       <c r="O31" s="16" t="n">
         <v>0</v>
@@ -2990,32 +2990,32 @@
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32732</t>
+          <t>PDMDEP-32759</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
+          <t>[COMMUNAUTE URBAINE DU GRAND REIMS - DSIT] - MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE LA SENTINELLE</t>
+          <t>COMMUNAUTE URBAINE DU GRAND REIMS - DSIT</t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Caisse</t>
+          <t>MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="F32" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G32" s="14" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I32" s="14" t="inlineStr">
@@ -3041,16 +3041,16 @@
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32741</t>
+          <t>PDMDEP-32763</t>
         </is>
       </c>
       <c r="M32" s="14" t="inlineStr">
         <is>
-          <t>00163789</t>
+          <t>00163805</t>
         </is>
       </c>
       <c r="N32" s="15" t="n">
-        <v>2138.2</v>
+        <v>564</v>
       </c>
       <c r="O32" s="16" t="n">
         <v>0</v>
@@ -3062,12 +3062,12 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32703</t>
+          <t>PDMDEP-32732</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[MAIRIE DE MIRIBEL] - MIGRATION PLACIER SIMPLE + PAX </t>
+          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
@@ -3077,12 +3077,12 @@
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE MIRIBEL</t>
+          <t>MAIRIE DE LA SENTINELLE</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGRATION PLACIER SIMPLE + PAX </t>
+          <t>Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J33" s="11" t="n">
@@ -3113,16 +3113,16 @@
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32712</t>
+          <t>PDMDEP-32741</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>00163498</t>
+          <t>00163789</t>
         </is>
       </c>
       <c r="N33" s="12" t="n">
-        <v>283.5</v>
+        <v>2138.2</v>
       </c>
       <c r="O33" s="16" t="n">
         <v>0</v>
@@ -3134,32 +3134,32 @@
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32625</t>
+          <t>PDMDEP-32703</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Modélisation LiEx</t>
+          <t xml:space="preserve">[MAIRIE DE MIRIBEL] - MIGRATION PLACIER SIMPLE + PAX </t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANTIBES</t>
+          <t>MAIRIE DE MIRIBEL</t>
         </is>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t xml:space="preserve">MIGRATION PLACIER SIMPLE + PAX </t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
@@ -3169,32 +3169,32 @@
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="J34" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K34" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32629</t>
+          <t>PDMDEP-32712</t>
         </is>
       </c>
       <c r="M34" s="14" t="inlineStr">
         <is>
-          <t>00163182</t>
+          <t>00163498</t>
         </is>
       </c>
       <c r="N34" s="15" t="n">
-        <v>548.4</v>
+        <v>283.5</v>
       </c>
       <c r="O34" s="16" t="n">
         <v>0</v>
@@ -3206,32 +3206,32 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32598</t>
+          <t>PDMDEP-32625</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
+          <t>[ANTIBES] - Modélisation LiEx</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>Déploiement GeoDP Caisse</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G35" s="11" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
@@ -3253,20 +3253,20 @@
         <v>3</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L35" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32607</t>
+          <t>PDMDEP-32629</t>
         </is>
       </c>
       <c r="M35" s="11" t="inlineStr">
         <is>
-          <t>00163155</t>
+          <t>00163182</t>
         </is>
       </c>
       <c r="N35" s="12" t="n">
-        <v>552</v>
+        <v>548.4</v>
       </c>
       <c r="O35" s="16" t="n">
         <v>0</v>
@@ -3278,27 +3278,27 @@
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32598</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
         </is>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="F36" s="14" t="inlineStr">
@@ -3313,32 +3313,32 @@
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J36" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K36" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32607</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00163155</t>
         </is>
       </c>
       <c r="N36" s="15" t="n">
-        <v>1868</v>
+        <v>552</v>
       </c>
       <c r="O36" s="16" t="n">
         <v>0</v>
@@ -3350,27 +3350,27 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32442</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod </t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
@@ -3390,27 +3390,27 @@
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J37" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K37" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32446</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>00161842</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N37" s="12" t="n">
-        <v>882.5</v>
+        <v>142.1</v>
       </c>
       <c r="O37" s="16" t="n">
         <v>0</v>
@@ -3422,27 +3422,27 @@
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F38" s="14" t="inlineStr">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J38" s="14" t="n">
@@ -3473,16 +3473,16 @@
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M38" s="14" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N38" s="15" t="n">
-        <v>450</v>
+        <v>1868</v>
       </c>
       <c r="O38" s="16" t="n">
         <v>0</v>
@@ -3494,12 +3494,12 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32442</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t xml:space="preserve">[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
@@ -3534,27 +3534,27 @@
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="J39" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32446</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161842</t>
         </is>
       </c>
       <c r="N39" s="12" t="n">
-        <v>1046.5</v>
+        <v>882.5</v>
       </c>
       <c r="O39" s="16" t="n">
         <v>0</v>
@@ -3566,32 +3566,32 @@
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32121</t>
+          <t>PDMDEP-32400</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
+          <t>[SM GESTION DES ROUTES DE GUADELOUPE] - Littéralis Expert - Interface Parapheur Ixbus</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARAN</t>
+          <t>SM GESTION DES ROUTES DE GUADELOUPE</t>
         </is>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE + Exp Ciril</t>
+          <t>Littéralis Expert - Interface Parapheur Ixbus</t>
         </is>
       </c>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I40" s="14" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="J40" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K40" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32128</t>
+          <t>PDMDEP-32406</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
         <is>
-          <t>00160621</t>
+          <t>00161680</t>
         </is>
       </c>
       <c r="N40" s="15" t="n">
-        <v>250</v>
-      </c>
-      <c r="O40" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P40" s="15" t="n">
@@ -3638,12 +3638,12 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
@@ -3653,12 +3653,12 @@
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J41" s="11" t="n">
@@ -3689,16 +3689,16 @@
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N41" s="12" t="n">
-        <v>407</v>
+        <v>450</v>
       </c>
       <c r="O41" s="16" t="n">
         <v>0</v>
@@ -3710,12 +3710,12 @@
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="D42" s="14" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F42" s="14" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I42" s="14" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J42" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K42" s="14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
         <is>
-          <t>00160148</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N42" s="15" t="n">
-        <v>440.38</v>
+        <v>1046.5</v>
       </c>
       <c r="O42" s="16" t="n">
         <v>0</v>
@@ -3782,27 +3782,27 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
@@ -3817,12 +3817,12 @@
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J43" s="11" t="n">
@@ -3833,16 +3833,16 @@
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N43" s="12" t="n">
-        <v>285</v>
+        <v>250</v>
       </c>
       <c r="O43" s="16" t="n">
         <v>0</v>
@@ -3854,32 +3854,32 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J44" s="14" t="n">
@@ -3905,16 +3905,16 @@
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N44" s="15" t="n">
-        <v>2650</v>
+        <v>407</v>
       </c>
       <c r="O44" s="16" t="n">
         <v>0</v>
@@ -3926,12 +3926,12 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J45" s="11" t="n">
@@ -3977,16 +3977,16 @@
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N45" s="12" t="n">
-        <v>120</v>
+        <v>440.38</v>
       </c>
       <c r="O45" s="16" t="n">
         <v>0</v>
@@ -3998,27 +3998,27 @@
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
@@ -4033,32 +4033,32 @@
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I46" s="14" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J46" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K46" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N46" s="15" t="n">
-        <v>203.5</v>
+        <v>285</v>
       </c>
       <c r="O46" s="16" t="n">
         <v>0</v>
@@ -4070,32 +4070,32 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G47" s="11" t="inlineStr">
@@ -4105,32 +4105,32 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J47" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K47" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N47" s="12" t="n">
-        <v>150</v>
+        <v>2650</v>
       </c>
       <c r="O47" s="16" t="n">
         <v>0</v>
@@ -4142,12 +4142,12 @@
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F48" s="14" t="inlineStr">
@@ -4182,27 +4182,27 @@
       </c>
       <c r="I48" s="14" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J48" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K48" s="14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N48" s="15" t="n">
-        <v>3288.55</v>
+        <v>120</v>
       </c>
       <c r="O48" s="16" t="n">
         <v>0</v>
@@ -4214,32 +4214,32 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31464</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>[CD 17] - Modélisation PV - 2 jours</t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G49" s="11" t="inlineStr">
@@ -4249,34 +4249,34 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J49" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K49" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31468</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>00157346</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" s="12" t="n">
+        <v>203.5</v>
+      </c>
+      <c r="O49" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P49" s="12" t="n">
@@ -4286,27 +4286,27 @@
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D50" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F50" s="14" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J50" s="14" t="n">
@@ -4337,16 +4337,16 @@
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31596</t>
         </is>
       </c>
       <c r="M50" s="14" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157967</t>
         </is>
       </c>
       <c r="N50" s="15" t="n">
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="O50" s="16" t="n">
         <v>0</v>
@@ -4358,27 +4358,27 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31285</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LUNEL] - FDS pour Littéralis Expert. Déjà chiffré en amont dans le ticket 1333</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Valentin CAUJOLLE</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LUNEL</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>FDS pour Littéralis Expert. Déjà chiffré en amont dans le ticket 1333</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
@@ -4398,27 +4398,27 @@
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J51" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31289</t>
+          <t>PDMDEP-31546</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>00156834</t>
+          <t>00157816</t>
         </is>
       </c>
       <c r="N51" s="12" t="n">
-        <v>71.2</v>
+        <v>3288.55</v>
       </c>
       <c r="O51" s="16" t="n">
         <v>0</v>
@@ -4430,32 +4430,32 @@
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31464</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[CD 17] - Modélisation PV - 2 jours</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
@@ -4465,34 +4465,34 @@
       </c>
       <c r="H52" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I52" s="14" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="J52" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K52" s="14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L52" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31468</t>
         </is>
       </c>
       <c r="M52" s="14" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00157346</t>
         </is>
       </c>
       <c r="N52" s="15" t="n">
-        <v>130</v>
-      </c>
-      <c r="O52" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P52" s="15" t="n">
@@ -4502,12 +4502,12 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J53" s="11" t="n">
@@ -4553,16 +4553,16 @@
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N53" s="12" t="n">
-        <v>255</v>
+        <v>210</v>
       </c>
       <c r="O53" s="16" t="n">
         <v>0</v>
@@ -4574,32 +4574,32 @@
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30358</t>
+          <t>PDMDEP-31285</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
+          <t>[COMMUNE DE LUNEL] - FDS pour Littéralis Expert. Déjà chiffré en amont dans le ticket 1333</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Valentin CAUJOLLE</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARGELES-SUR-MER</t>
+          <t>COMMUNE DE LUNEL</t>
         </is>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>FDS pour Littéralis Expert. Déjà chiffré en amont dans le ticket 1333</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
@@ -4609,32 +4609,32 @@
       </c>
       <c r="H54" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I54" s="14" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>16/02/2026</t>
         </is>
       </c>
       <c r="J54" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K54" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30366</t>
+          <t>PDMDEP-31289</t>
         </is>
       </c>
       <c r="M54" s="14" t="inlineStr">
         <is>
-          <t>00154569</t>
+          <t>00156834</t>
         </is>
       </c>
       <c r="N54" s="15" t="n">
-        <v>1000</v>
+        <v>71.2</v>
       </c>
       <c r="O54" s="16" t="n">
         <v>0</v>
@@ -4646,12 +4646,12 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
@@ -4686,27 +4686,27 @@
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J55" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K55" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N55" s="12" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="O55" s="16" t="n">
         <v>0</v>
@@ -4718,27 +4718,27 @@
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30311</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CAEN] - GeODP - Modification des marges via activation Editique</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAEN</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>GeODP - Modification des marges via activation Editique</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F56" s="14" t="inlineStr">
@@ -4758,27 +4758,27 @@
       </c>
       <c r="I56" s="14" t="inlineStr">
         <is>
-          <t>27/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J56" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K56" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L56" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30316</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M56" s="14" t="inlineStr">
         <is>
-          <t>00154362</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N56" s="15" t="n">
-        <v>200</v>
+        <v>255</v>
       </c>
       <c r="O56" s="16" t="n">
         <v>0</v>
@@ -4790,32 +4790,32 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30358</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE D'ARGELES-SUR-MER</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G57" s="11" t="inlineStr">
@@ -4825,34 +4825,34 @@
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="J57" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K57" s="11" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30366</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00154569</t>
         </is>
       </c>
       <c r="N57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" s="12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="O57" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P57" s="12" t="n">
@@ -4862,32 +4862,32 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30062</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Saint-Dizier] - Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>Commune de Saint-Dizier</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G58" s="14" t="inlineStr">
@@ -4897,32 +4897,32 @@
       </c>
       <c r="H58" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
-          <t>19/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J58" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K58" s="14" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L58" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30063</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M58" s="14" t="inlineStr">
         <is>
-          <t>00153633</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N58" s="15" t="n">
-        <v>350</v>
+        <v>140</v>
       </c>
       <c r="O58" s="16" t="n">
         <v>0</v>
@@ -4934,32 +4934,32 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29948</t>
+          <t>PDMDEP-30311</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
+          <t>[COMMUNE DE CAEN] - GeODP - Modification des marges via activation Editique</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>MAIRE DE PONTARLIER</t>
+          <t>COMMUNE DE CAEN</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>Projet d'options supplémentaires Littéralis Expert</t>
+          <t>GeODP - Modification des marges via activation Editique</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G59" s="11" t="inlineStr">
@@ -4969,34 +4969,34 @@
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>27/01/2026</t>
         </is>
       </c>
       <c r="J59" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29949</t>
+          <t>PDMDEP-30316</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
         <is>
-          <t>00152726</t>
+          <t>00154362</t>
         </is>
       </c>
       <c r="N59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" s="12" t="n">
+        <v>200</v>
+      </c>
+      <c r="O59" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P59" s="12" t="n">
@@ -5006,27 +5006,27 @@
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F60" s="14" t="inlineStr">
@@ -5046,23 +5046,23 @@
       </c>
       <c r="I60" s="14" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J60" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K60" s="14" t="n">
-        <v>0.08</v>
+        <v>0.75</v>
       </c>
       <c r="L60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30431</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M60" s="14" t="inlineStr">
         <is>
-          <t>00154684</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N60" s="15" t="n">
@@ -5078,27 +5078,27 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30062</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[Commune de Saint-Dizier] - Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>Commune de Saint-Dizier</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
@@ -5118,29 +5118,29 @@
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>19/01/2026</t>
         </is>
       </c>
       <c r="J61" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>0.08</v>
+        <v>0.75</v>
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-30063</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00153633</t>
         </is>
       </c>
       <c r="N61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" s="12" t="n">
+        <v>350</v>
+      </c>
+      <c r="O61" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P61" s="12" t="n">
@@ -5150,12 +5150,12 @@
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-29948</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>MAIRE DE PONTARLIER</t>
         </is>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Projet d'options supplémentaires Littéralis Expert</t>
         </is>
       </c>
       <c r="F62" s="14" t="inlineStr">
@@ -5190,23 +5190,23 @@
       </c>
       <c r="I62" s="14" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J62" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K62" s="14" t="n">
-        <v>0.08</v>
+        <v>1</v>
       </c>
       <c r="L62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-29949</t>
         </is>
       </c>
       <c r="M62" s="14" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00152726</t>
         </is>
       </c>
       <c r="N62" s="15" t="n">
@@ -5222,26 +5222,28 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29122</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DES DEUX SEVRES (CD 79) - LITTERALIS - Flux WFS communication</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DES DEUX SEVRES (CD 79)</t>
-        </is>
-      </c>
-      <c r="E63" s="11" t="n">
-        <v/>
+          <t>COMMUNE DE BIARRITZ</t>
+        </is>
+      </c>
+      <c r="E63" s="11" t="inlineStr">
+        <is>
+          <t>Paramétrages complémentaires + Vision</t>
+        </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
@@ -5260,29 +5262,29 @@
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>19/12/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J63" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="L63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29124</t>
+          <t>PDMDEP-30431</t>
         </is>
       </c>
       <c r="M63" s="11" t="inlineStr">
         <is>
-          <t>00148148</t>
+          <t>00154684</t>
         </is>
       </c>
       <c r="N63" s="12" t="n">
-        <v>157.5</v>
-      </c>
-      <c r="O63" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P63" s="12" t="n">
@@ -5292,26 +5294,28 @@
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D64" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E64" s="14" t="n">
-        <v/>
+          <t>COMMUNE DE BIARRITZ</t>
+        </is>
+      </c>
+      <c r="E64" s="14" t="inlineStr">
+        <is>
+          <t>Paramétrages complémentaires + Vision</t>
+        </is>
       </c>
       <c r="F64" s="14" t="inlineStr">
         <is>
@@ -5325,34 +5329,34 @@
       </c>
       <c r="H64" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I64" s="14" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J64" s="14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K64" s="14" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="L64" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M64" s="14" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N64" s="15" t="n">
-        <v>2812.32</v>
-      </c>
-      <c r="O64" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P64" s="15" t="n">
@@ -5362,27 +5366,27 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
@@ -5397,34 +5401,34 @@
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J65" s="11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>0.45</v>
+        <v>0.08</v>
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N65" s="12" t="n">
-        <v>392.5</v>
-      </c>
-      <c r="O65" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P65" s="12" t="n">
@@ -5434,12 +5438,12 @@
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-29122</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>DEPARTEMENT DES DEUX SEVRES (CD 79) - LITTERALIS - Flux WFS communication</t>
         </is>
       </c>
       <c r="C66" s="14" t="inlineStr">
@@ -5449,13 +5453,11 @@
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E66" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>DEPARTEMENT DES DEUX SEVRES (CD 79)</t>
+        </is>
+      </c>
+      <c r="E66" s="14" t="n">
+        <v/>
       </c>
       <c r="F66" s="14" t="inlineStr">
         <is>
@@ -5469,32 +5471,32 @@
       </c>
       <c r="H66" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I66" s="14" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>19/12/2025</t>
         </is>
       </c>
       <c r="J66" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K66" s="14" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="L66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-29124</t>
         </is>
       </c>
       <c r="M66" s="14" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00148148</t>
         </is>
       </c>
       <c r="N66" s="15" t="n">
-        <v>1556.25</v>
+        <v>157.5</v>
       </c>
       <c r="O66" s="16" t="n">
         <v>0</v>
@@ -5506,12 +5508,12 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
@@ -5521,13 +5523,11 @@
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E67" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E67" s="11" t="n">
+        <v/>
       </c>
       <c r="F67" s="11" t="inlineStr">
         <is>
@@ -5546,27 +5546,27 @@
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J67" s="11" t="n">
         <v>8</v>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
-        <v>1790</v>
+        <v>2812.32</v>
       </c>
       <c r="O67" s="16" t="n">
         <v>0</v>
@@ -5625,22 +5625,22 @@
         <v>8</v>
       </c>
       <c r="K68" s="14" t="n">
-        <v>0.45</v>
+        <v>0.25</v>
       </c>
       <c r="L68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M68" s="14" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N68" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O68" s="15" t="n">
+        <v>392.5</v>
+      </c>
+      <c r="O68" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P68" s="15" t="n">
@@ -5697,22 +5697,22 @@
         <v>8</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>0.45</v>
+        <v>0.25</v>
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N69" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O69" s="12" t="n">
+        <v>1556.25</v>
+      </c>
+      <c r="O69" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P69" s="12" t="n">
@@ -5722,12 +5722,12 @@
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-27634</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C70" s="14" t="inlineStr">
@@ -5737,11 +5737,13 @@
       </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
-        </is>
-      </c>
-      <c r="E70" s="14" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E70" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F70" s="14" t="inlineStr">
         <is>
@@ -5755,34 +5757,34 @@
       </c>
       <c r="H70" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I70" s="14" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J70" s="14" t="n">
         <v>8</v>
       </c>
       <c r="K70" s="14" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27642</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M70" s="14" t="inlineStr">
         <is>
-          <t>00143935</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N70" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O70" s="15" t="n">
+        <v>1790</v>
+      </c>
+      <c r="O70" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P70" s="15" t="n">
@@ -5792,12 +5794,12 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
@@ -5807,11 +5809,13 @@
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
-        </is>
-      </c>
-      <c r="E71" s="11" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E71" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
@@ -5830,29 +5834,29 @@
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J71" s="11" t="n">
         <v>8</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>2.5</v>
+        <v>0.25</v>
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M71" s="11" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N71" s="12" t="n">
-        <v>732</v>
-      </c>
-      <c r="O71" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P71" s="12" t="n">
@@ -5862,27 +5866,27 @@
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-26782</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C72" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t>Déploiement LiEx</t>
+          <t>Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="F72" s="14" t="inlineStr">
@@ -5902,7 +5906,7 @@
       </c>
       <c r="I72" s="14" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J72" s="14" t="n">
@@ -5913,12 +5917,12 @@
       </c>
       <c r="L72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-26783</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M72" s="14" t="inlineStr">
         <is>
-          <t>00142659</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N72" s="15" t="n">
@@ -5934,12 +5938,12 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
@@ -5949,7 +5953,7 @@
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
         </is>
       </c>
       <c r="E73" s="11" t="n">
@@ -5967,34 +5971,34 @@
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J73" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-27642</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00143935</t>
         </is>
       </c>
       <c r="N73" s="12" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O73" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P73" s="12" t="n">
@@ -6004,22 +6008,22 @@
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24426</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>[DRANCY] - Migration STD vers Exp</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C74" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE DRANCY</t>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
         </is>
       </c>
       <c r="E74" s="14" t="n">
@@ -6037,34 +6041,34 @@
       </c>
       <c r="H74" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I74" s="14" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J74" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K74" s="14" t="n">
-        <v>0.25</v>
+        <v>2.5</v>
       </c>
       <c r="L74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27028</t>
+          <t>PDMDEP-27557</t>
         </is>
       </c>
       <c r="M74" s="14" t="inlineStr">
         <is>
-          <t>500950</t>
+          <t>00144532</t>
         </is>
       </c>
       <c r="N74" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O74" s="15" t="n">
+        <v>732</v>
+      </c>
+      <c r="O74" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P74" s="15" t="n">
@@ -6074,26 +6078,28 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-26782</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
-        </is>
-      </c>
-      <c r="E75" s="11" t="n">
-        <v/>
+          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
+        </is>
+      </c>
+      <c r="E75" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement LiEx</t>
+        </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
         <is>
@@ -6112,29 +6118,29 @@
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="J75" s="11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-26783</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>00142659</t>
         </is>
       </c>
       <c r="N75" s="12" t="n">
-        <v>2323</v>
-      </c>
-      <c r="O75" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P75" s="12" t="n">
@@ -6144,22 +6150,22 @@
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-23484</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON- AJOUT LIEU DE NAISSANCE DANS FILIEN</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C76" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
         </is>
       </c>
       <c r="E76" s="14" t="n">
@@ -6167,7 +6173,7 @@
       </c>
       <c r="F76" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G76" s="14" t="inlineStr">
@@ -6177,32 +6183,32 @@
       </c>
       <c r="H76" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I76" s="14" t="inlineStr">
         <is>
-          <t>25/07/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J76" s="14" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K76" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27494</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M76" s="14" t="inlineStr">
         <is>
-          <t>495695</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N76" s="15" t="n">
-        <v>140.4</v>
+        <v>1212</v>
       </c>
       <c r="O76" s="16" t="n">
         <v>0</v>
@@ -6214,12 +6220,12 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-22996</t>
+          <t>PDMDEP-24426</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
+          <t>[DRANCY] - Migration STD vers Exp</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
@@ -6229,7 +6235,7 @@
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>VILLE DE DRANCY</t>
         </is>
       </c>
       <c r="E77" s="11" t="n">
@@ -6252,23 +6258,23 @@
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="J77" s="11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28051</t>
+          <t>PDMDEP-27028</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>487190</t>
+          <t>500950</t>
         </is>
       </c>
       <c r="N77" s="12" t="n">
@@ -6284,22 +6290,22 @@
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21546</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>[Villeurbanne] Evolution produit - impression des tickets d'infraction et de présence</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C78" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D78" s="14" t="inlineStr">
         <is>
-          <t>VILLEURBANNE</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E78" s="14" t="n">
@@ -6307,7 +6313,7 @@
       </c>
       <c r="F78" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G78" s="14" t="inlineStr">
@@ -6317,32 +6323,32 @@
       </c>
       <c r="H78" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I78" s="14" t="inlineStr">
         <is>
-          <t>05/05/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J78" s="14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K78" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28038</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M78" s="14" t="inlineStr">
         <is>
-          <t>478867</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N78" s="15" t="n">
-        <v>1413.6</v>
+        <v>2323</v>
       </c>
       <c r="O78" s="16" t="n">
         <v>0</v>
@@ -6354,22 +6360,22 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-23484</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>METROPOLE TOULON- AJOUT LIEU DE NAISSANCE DANS FILIEN</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E79" s="11" t="n">
@@ -6377,7 +6383,7 @@
       </c>
       <c r="F79" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G79" s="11" t="inlineStr">
@@ -6392,27 +6398,27 @@
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>25/07/2025</t>
         </is>
       </c>
       <c r="J79" s="11" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K79" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-27494</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>495695</t>
         </is>
       </c>
       <c r="N79" s="12" t="n">
-        <v>250</v>
+        <v>140.4</v>
       </c>
       <c r="O79" s="16" t="n">
         <v>0</v>
@@ -6424,12 +6430,12 @@
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-22996</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
         </is>
       </c>
       <c r="C80" s="14" t="inlineStr">
@@ -6439,7 +6445,7 @@
       </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E80" s="14" t="n">
@@ -6462,29 +6468,29 @@
       </c>
       <c r="I80" s="14" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>07/07/2025</t>
         </is>
       </c>
       <c r="J80" s="14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K80" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28051</t>
         </is>
       </c>
       <c r="M80" s="14" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>487190</t>
         </is>
       </c>
       <c r="N80" s="15" t="n">
-        <v>460</v>
-      </c>
-      <c r="O80" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P80" s="15" t="n">
@@ -6494,22 +6500,22 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-19792</t>
+          <t>PDMDEP-21546</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+          <t>[Villeurbanne] Evolution produit - impression des tickets d'infraction et de présence</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+          <t>VILLEURBANNE</t>
         </is>
       </c>
       <c r="E81" s="11" t="n">
@@ -6517,7 +6523,7 @@
       </c>
       <c r="F81" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G81" s="11" t="inlineStr">
@@ -6527,34 +6533,34 @@
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>06/03/2025</t>
+          <t>05/05/2025</t>
         </is>
       </c>
       <c r="J81" s="11" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27377</t>
+          <t>PDMDEP-28038</t>
         </is>
       </c>
       <c r="M81" s="11" t="inlineStr">
         <is>
-          <t>478048</t>
+          <t>478867</t>
         </is>
       </c>
       <c r="N81" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" s="12" t="n">
+        <v>1413.6</v>
+      </c>
+      <c r="O81" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P81" s="12" t="n">
@@ -6564,22 +6570,22 @@
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-19385</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C82" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARCUEIL</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E82" s="14" t="n">
@@ -6597,34 +6603,34 @@
       </c>
       <c r="H82" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I82" s="14" t="inlineStr">
         <is>
-          <t>24/02/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J82" s="14" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K82" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27535</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M82" s="14" t="inlineStr">
         <is>
-          <t>465345</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N82" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O82" s="15" t="n">
+        <v>250</v>
+      </c>
+      <c r="O82" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P82" s="15" t="n">
@@ -6634,22 +6640,22 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E83" s="11" t="n">
@@ -6657,7 +6663,7 @@
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G83" s="11" t="inlineStr">
@@ -6667,32 +6673,32 @@
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J83" s="11" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28019</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M83" s="11" t="inlineStr">
         <is>
-          <t>455151</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N83" s="12" t="n">
-        <v>240</v>
+        <v>460</v>
       </c>
       <c r="O83" s="16" t="n">
         <v>0</v>
@@ -6704,12 +6710,12 @@
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C84" s="14" t="inlineStr">
@@ -6719,7 +6725,7 @@
       </c>
       <c r="D84" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E84" s="14" t="n">
@@ -6742,23 +6748,23 @@
       </c>
       <c r="I84" s="14" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J84" s="14" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K84" s="14" t="n">
         <v>0.25</v>
       </c>
       <c r="L84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28020</t>
+          <t>PDMDEP-27568</t>
         </is>
       </c>
       <c r="M84" s="14" t="inlineStr">
         <is>
-          <t>458057</t>
+          <t>471958</t>
         </is>
       </c>
       <c r="N84" s="15" t="n">
@@ -6774,22 +6780,22 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-16868</t>
+          <t>PDMDEP-19792</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>[Limoges] migration placier</t>
+          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>Limoges</t>
+          <t>VIENNE CONDRIEU AGGLOMERATION</t>
         </is>
       </c>
       <c r="E85" s="11" t="n">
@@ -6797,32 +6803,40 @@
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G85" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>26/09/2024</t>
+          <t>06/03/2025</t>
         </is>
       </c>
       <c r="J85" s="11" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="K85" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L85" s="11" t="inlineStr"/>
-      <c r="M85" s="11" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L85" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27377</t>
+        </is>
+      </c>
+      <c r="M85" s="11" t="inlineStr">
+        <is>
+          <t>478048</t>
+        </is>
+      </c>
       <c r="N85" s="12" t="n">
         <v>0</v>
       </c>
@@ -6836,12 +6850,12 @@
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-14551</t>
+          <t>PDMDEP-19385</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>[Perpignan] Interface formulaire</t>
+          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
         </is>
       </c>
       <c r="C86" s="14" t="inlineStr">
@@ -6851,7 +6865,7 @@
       </c>
       <c r="D86" s="14" t="inlineStr">
         <is>
-          <t>[Perpignan]</t>
+          <t>COMMUNE D'ARCUEIL</t>
         </is>
       </c>
       <c r="E86" s="14" t="n">
@@ -6864,27 +6878,35 @@
       </c>
       <c r="G86" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H86" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I86" s="14" t="inlineStr">
         <is>
-          <t>14/03/2024</t>
+          <t>24/02/2025</t>
         </is>
       </c>
       <c r="J86" s="14" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="K86" s="14" t="n">
         <v>0.25</v>
       </c>
-      <c r="L86" s="14" t="inlineStr"/>
-      <c r="M86" s="14" t="inlineStr"/>
+      <c r="L86" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27535</t>
+        </is>
+      </c>
+      <c r="M86" s="14" t="inlineStr">
+        <is>
+          <t>465345</t>
+        </is>
+      </c>
       <c r="N86" s="15" t="n">
         <v>0</v>
       </c>
@@ -6898,12 +6920,12 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
@@ -6913,13 +6935,11 @@
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E87" s="11" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t>Biarritz</t>
+        </is>
+      </c>
+      <c r="E87" s="11" t="n">
+        <v/>
       </c>
       <c r="F87" s="11" t="inlineStr">
         <is>
@@ -6933,19 +6953,19 @@
       </c>
       <c r="H87" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J87" s="11" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="L87" s="11" t="inlineStr"/>
       <c r="M87" s="11" t="inlineStr"/>
@@ -6962,57 +6982,67 @@
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C88" s="14" t="inlineStr"/>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
+        </is>
+      </c>
+      <c r="C88" s="14" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
       <c r="D88" s="14" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E88" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>BISCHWILLER</t>
+        </is>
+      </c>
+      <c r="E88" s="14" t="n">
+        <v/>
       </c>
       <c r="F88" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G88" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H88" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J88" s="14" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="K88" s="14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L88" s="14" t="inlineStr"/>
-      <c r="M88" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L88" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28019</t>
+        </is>
+      </c>
+      <c r="M88" s="14" t="inlineStr">
+        <is>
+          <t>455151</t>
+        </is>
+      </c>
       <c r="N88" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O88" s="15" t="n">
+        <v>240</v>
+      </c>
+      <c r="O88" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P88" s="15" t="n">
@@ -7022,21 +7052,27 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
-        </is>
-      </c>
-      <c r="C89" s="11" t="inlineStr"/>
+          <t>[CD 38] Reprise de 1644 AP</t>
+        </is>
+      </c>
+      <c r="C89" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
-        </is>
-      </c>
-      <c r="E89" s="11" t="inlineStr"/>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+        </is>
+      </c>
+      <c r="E89" s="11" t="n">
+        <v/>
+      </c>
       <c r="F89" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -7047,32 +7083,36 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H89" s="11" t="inlineStr"/>
+      <c r="H89" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J89" s="11" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="K89" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33362</t>
+          <t>PDMDEP-28020</t>
         </is>
       </c>
       <c r="M89" s="11" t="inlineStr">
         <is>
-          <t>00167140</t>
+          <t>458057</t>
         </is>
       </c>
       <c r="N89" s="12" t="n">
-        <v>510.6</v>
-      </c>
-      <c r="O89" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P89" s="12" t="n">
@@ -7082,89 +7122,531 @@
     <row r="90">
       <c r="A90" s="13" t="inlineStr">
         <is>
+          <t>PDMDEP-16868</t>
+        </is>
+      </c>
+      <c r="B90" s="14" t="inlineStr">
+        <is>
+          <t>[Limoges] migration placier</t>
+        </is>
+      </c>
+      <c r="C90" s="14" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="D90" s="14" t="inlineStr">
+        <is>
+          <t>Limoges</t>
+        </is>
+      </c>
+      <c r="E90" s="14" t="n">
+        <v/>
+      </c>
+      <c r="F90" s="14" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="G90" s="14" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H90" s="14" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="I90" s="14" t="inlineStr">
+        <is>
+          <t>26/09/2024</t>
+        </is>
+      </c>
+      <c r="J90" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="K90" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L90" s="14" t="inlineStr"/>
+      <c r="M90" s="14" t="inlineStr"/>
+      <c r="N90" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-14551</t>
+        </is>
+      </c>
+      <c r="B91" s="11" t="inlineStr">
+        <is>
+          <t>[Perpignan] Interface formulaire</t>
+        </is>
+      </c>
+      <c r="C91" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D91" s="11" t="inlineStr">
+        <is>
+          <t>[Perpignan]</t>
+        </is>
+      </c>
+      <c r="E91" s="11" t="n">
+        <v/>
+      </c>
+      <c r="F91" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G91" s="11" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H91" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I91" s="11" t="inlineStr">
+        <is>
+          <t>14/03/2024</t>
+        </is>
+      </c>
+      <c r="J91" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="K91" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L91" s="11" t="inlineStr"/>
+      <c r="M91" s="11" t="inlineStr"/>
+      <c r="N91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-12747</t>
+        </is>
+      </c>
+      <c r="B92" s="14" t="inlineStr">
+        <is>
+          <t>[FOUGERES] ARPEGE</t>
+        </is>
+      </c>
+      <c r="C92" s="14" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D92" s="14" t="inlineStr">
+        <is>
+          <t>FOUGERES</t>
+        </is>
+      </c>
+      <c r="E92" s="14" t="n">
+        <v/>
+      </c>
+      <c r="F92" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G92" s="14" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H92" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I92" s="14" t="inlineStr">
+        <is>
+          <t>26/09/2023</t>
+        </is>
+      </c>
+      <c r="J92" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="K92" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L92" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M92" s="14" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
+      <c r="N92" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-12241</t>
+        </is>
+      </c>
+      <c r="B93" s="11" t="inlineStr">
+        <is>
+          <t>[SM Routes de Guadeloupe] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C93" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D93" s="11" t="inlineStr">
+        <is>
+          <t>[SM Routes de Guadeloupe]</t>
+        </is>
+      </c>
+      <c r="E93" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement de Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="F93" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G93" s="11" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H93" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I93" s="11" t="inlineStr">
+        <is>
+          <t>04/09/2023</t>
+        </is>
+      </c>
+      <c r="J93" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="K93" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L93" s="11" t="inlineStr"/>
+      <c r="M93" s="11" t="inlineStr"/>
+      <c r="N93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-12222</t>
+        </is>
+      </c>
+      <c r="B94" s="14" t="inlineStr">
+        <is>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C94" s="14" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D94" s="14" t="inlineStr">
+        <is>
+          <t>CD14</t>
+        </is>
+      </c>
+      <c r="E94" s="14" t="inlineStr">
+        <is>
+          <t>Modélisation spécifique</t>
+        </is>
+      </c>
+      <c r="F94" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G94" s="14" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H94" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I94" s="14" t="inlineStr">
+        <is>
+          <t>04/09/2023</t>
+        </is>
+      </c>
+      <c r="J94" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="K94" s="14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L94" s="14" t="inlineStr"/>
+      <c r="M94" s="14" t="inlineStr"/>
+      <c r="N94" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-11477</t>
+        </is>
+      </c>
+      <c r="B95" s="11" t="inlineStr">
+        <is>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C95" s="11" t="inlineStr"/>
+      <c r="D95" s="11" t="inlineStr">
+        <is>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E95" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
+      <c r="F95" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G95" s="11" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H95" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I95" s="11" t="inlineStr">
+        <is>
+          <t>03/09/2023</t>
+        </is>
+      </c>
+      <c r="J95" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="K95" s="11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L95" s="11" t="inlineStr"/>
+      <c r="M95" s="11" t="inlineStr"/>
+      <c r="N95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="13" t="inlineStr">
+        <is>
+          <t>PSC-1270</t>
+        </is>
+      </c>
+      <c r="B96" s="14" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="C96" s="14" t="inlineStr"/>
+      <c r="D96" s="14" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="E96" s="14" t="inlineStr"/>
+      <c r="F96" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G96" s="14" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H96" s="14" t="inlineStr"/>
+      <c r="I96" s="14" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="J96" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K96" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M96" s="14" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
+      <c r="N96" s="15" t="n">
+        <v>510.6</v>
+      </c>
+      <c r="O96" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="10" t="inlineStr">
+        <is>
           <t>PSC-1228</t>
         </is>
       </c>
-      <c r="B90" s="14" t="inlineStr">
+      <c r="B97" s="11" t="inlineStr">
         <is>
           <t>MAIRIE DE MERLEVENEZ</t>
         </is>
       </c>
-      <c r="C90" s="14" t="inlineStr"/>
-      <c r="D90" s="14" t="inlineStr">
+      <c r="C97" s="11" t="inlineStr"/>
+      <c r="D97" s="11" t="inlineStr">
         <is>
           <t>MAIRIE DE MERLEVENEZ</t>
         </is>
       </c>
-      <c r="E90" s="14" t="inlineStr"/>
-      <c r="F90" s="14" t="inlineStr">
+      <c r="E97" s="11" t="inlineStr"/>
+      <c r="F97" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="G90" s="14" t="inlineStr">
+      <c r="G97" s="11" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H90" s="14" t="inlineStr"/>
-      <c r="I90" s="14" t="inlineStr">
+      <c r="H97" s="11" t="inlineStr"/>
+      <c r="I97" s="11" t="inlineStr">
         <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="J90" s="14" t="n">
+      <c r="J97" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="K90" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" s="14" t="inlineStr">
+      <c r="K97" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" s="11" t="inlineStr">
         <is>
           <t>PDMDEP-32829</t>
         </is>
       </c>
-      <c r="M90" s="14" t="inlineStr">
+      <c r="M97" s="11" t="inlineStr">
         <is>
           <t>00163534</t>
         </is>
       </c>
-      <c r="N90" s="15" t="n">
+      <c r="N97" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="O90" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="17" t="inlineStr">
+      <c r="O97" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B91" s="17" t="inlineStr"/>
-      <c r="C91" s="17" t="inlineStr"/>
-      <c r="D91" s="17" t="inlineStr"/>
-      <c r="E91" s="17" t="inlineStr"/>
-      <c r="F91" s="17" t="inlineStr"/>
-      <c r="G91" s="17" t="inlineStr"/>
-      <c r="H91" s="17" t="inlineStr"/>
-      <c r="I91" s="17" t="inlineStr"/>
-      <c r="J91" s="17" t="inlineStr"/>
-      <c r="K91" s="17" t="inlineStr"/>
-      <c r="L91" s="17" t="inlineStr"/>
-      <c r="M91" s="17" t="inlineStr"/>
-      <c r="N91" s="18" t="n">
-        <v>56751.68</v>
-      </c>
-      <c r="O91" s="18" t="n">
-        <v>1298.1</v>
-      </c>
-      <c r="P91" s="18" t="n">
-        <v>44.39</v>
+      <c r="B98" s="17" t="inlineStr"/>
+      <c r="C98" s="17" t="inlineStr"/>
+      <c r="D98" s="17" t="inlineStr"/>
+      <c r="E98" s="17" t="inlineStr"/>
+      <c r="F98" s="17" t="inlineStr"/>
+      <c r="G98" s="17" t="inlineStr"/>
+      <c r="H98" s="17" t="inlineStr"/>
+      <c r="I98" s="17" t="inlineStr"/>
+      <c r="J98" s="17" t="inlineStr"/>
+      <c r="K98" s="17" t="inlineStr"/>
+      <c r="L98" s="17" t="inlineStr"/>
+      <c r="M98" s="17" t="inlineStr"/>
+      <c r="N98" s="18" t="n">
+        <v>57120.64</v>
+      </c>
+      <c r="O98" s="18" t="n">
+        <v>2326.5</v>
+      </c>
+      <c r="P98" s="18" t="n">
+        <v>64.2</v>
       </c>
     </row>
   </sheetData>
@@ -7256,6 +7738,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId85"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId93"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7830,26 +8319,26 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>19.75</v>
+        <v>23.5</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="D5" s="14" t="n">
         <v>0.5</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>25.25</v>
+        <v>30.25</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>486.15</v>
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>6.2%</t>
         </is>
       </c>
     </row>
@@ -7860,7 +8349,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>2</v>
@@ -7869,17 +8358,17 @@
         <v>0</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" s="11" t="n">
         <v>263.34</v>
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>2.3%</t>
         </is>
       </c>
     </row>
@@ -7891,7 +8380,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>7.25</v>
+        <v>7.75</v>
       </c>
     </row>
   </sheetData>
@@ -7976,16 +8465,16 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>395260</v>
+        <v>394231</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>194001</v>
+        <v>192032</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>201259</v>
+        <v>202200</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>169899</v>
+        <v>170840</v>
       </c>
       <c r="F5" s="24" t="n">
         <v>15760</v>
@@ -8001,16 +8490,16 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>187891</v>
+        <v>186863</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>83887</v>
+        <v>81917</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>104005</v>
+        <v>104945</v>
       </c>
       <c r="E6" s="25" t="n">
-        <v>96496</v>
+        <v>97437</v>
       </c>
       <c r="F6" s="25" t="n">
         <v>3060</v>
@@ -8055,7 +8544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -8079,7 +8568,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 2 commande(s)</t>
+          <t>Épics créées ce mois — 3 commande(s)</t>
         </is>
       </c>
     </row>
@@ -8134,22 +8623,22 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34396</t>
+          <t>PDMDEP-34420</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34390</t>
+          <t>PDMDEP-34411</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>Commune Le THOR</t>
+          <t>MAIRIE DE MAIZIERES LES METZ</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -8159,7 +8648,7 @@
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -8169,7 +8658,7 @@
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>00171793</t>
+          <t>00172317</t>
         </is>
       </c>
       <c r="I5" s="25" t="n">
@@ -8179,73 +8668,97 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
+          <t>PDMDEP-34396</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34390</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>Commune Le THOR</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>00171793</t>
+        </is>
+      </c>
+      <c r="I6" s="26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
           <t>PDMDEP-34362</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>PDMDEP-34358</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>01/07/2026</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F7" s="14" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H7" s="14" t="inlineStr">
         <is>
           <t>458057</t>
         </is>
       </c>
-      <c r="I6" s="26" t="n">
+      <c r="I7" s="25" t="n">
         <v>6806.25</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="n"/>
-      <c r="C7" s="17" t="n"/>
-      <c r="D7" s="17" t="n"/>
-      <c r="E7" s="17" t="n"/>
-      <c r="F7" s="17" t="n"/>
-      <c r="G7" s="17" t="n"/>
-      <c r="H7" s="17" t="inlineStr">
-        <is>
-          <t>2 commande(s)</t>
-        </is>
-      </c>
-      <c r="I7" s="24" t="n">
-        <v>6806</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="17" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B8" s="17" t="n"/>
@@ -8256,7 +8769,7 @@
       <c r="G8" s="17" t="n"/>
       <c r="H8" s="17" t="inlineStr">
         <is>
-          <t>1 commande(s)</t>
+          <t>3 commande(s)</t>
         </is>
       </c>
       <c r="I8" s="24" t="n">
@@ -8266,7 +8779,7 @@
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B9" s="17" t="n"/>
@@ -8281,6 +8794,27 @@
         </is>
       </c>
       <c r="I9" s="24" t="n">
+        <v>6806</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
+      <c r="G10" s="17" t="n"/>
+      <c r="H10" s="17" t="inlineStr">
+        <is>
+          <t>2 commande(s)</t>
+        </is>
+      </c>
+      <c r="I10" s="24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8295,13 +8829,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
@@ -8316,7 +8850,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>0 clôture(s) : 0 projet(s), 0 rework</t>
+          <t>1 clôture(s) : 1 projet(s), 0 rework</t>
         </is>
       </c>
     </row>
@@ -8353,32 +8887,62 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-33720</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>[COMMUNE DE LEVALLOIS PERRET] - PRESTA PURGE DES ACTES EN UR</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>TOTAL projets clôturés</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n"/>
-      <c r="C6" s="17" t="n"/>
-      <c r="D6" s="17" t="n"/>
-      <c r="E6" s="17" t="n"/>
-      <c r="F6" s="17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>TOTAL rework clôturés</t>
         </is>
       </c>
-      <c r="B7" s="27" t="n"/>
-      <c r="C7" s="27" t="n"/>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="27" t="n"/>
-      <c r="F7" s="27" t="n">
+      <c r="B8" s="27" t="n"/>
+      <c r="C8" s="27" t="n"/>
+      <c r="D8" s="27" t="n"/>
+      <c r="E8" s="27" t="n"/>
+      <c r="F8" s="27" t="n">
         <v>0</v>
       </c>
     </row>

--- a/jira_export_2026-07-02.xlsx
+++ b/jira_export_2026-07-02.xlsx
@@ -729,7 +729,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>2,326 €</t>
+          <t>2,446 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -743,7 +743,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -769,7 +769,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>1,248 €</t>
+          <t>1,368 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -824,7 +824,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>61 h</t>
+          <t>73 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -838,7 +838,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>76.0%</t>
+          <t>91.0%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -895,7 +895,7 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B25" s="7" t="n"/>
@@ -942,7 +942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P105"/>
+  <dimension ref="A1:P108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1351,32 +1351,32 @@
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33906</t>
+          <t>PDMDEP-33949</t>
         </is>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
+          <t>[Commune de Colmar] - Modélisation Littéralis Expert</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Commune d'Arras</t>
+          <t>Commune de Colmar</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Migration GEODP ODP (Terrasse)</t>
+          <t>Modélisation Littéralis Expert</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G9" s="12" t="inlineStr">
@@ -1386,34 +1386,34 @@
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I9" s="12" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J9" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K9" s="12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="L9" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33914</t>
+          <t>PDMDEP-33955</t>
         </is>
       </c>
       <c r="M9" s="12" t="inlineStr">
         <is>
-          <t>00167633</t>
+          <t>00170302</t>
         </is>
       </c>
       <c r="N9" s="13" t="n">
-        <v>2100</v>
-      </c>
-      <c r="O9" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P9" s="13" t="n">
@@ -1423,27 +1423,27 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33841</t>
+          <t>PDMDEP-33906</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>Commune de Nans les Pins</t>
+          <t>Commune d'Arras</t>
         </is>
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="F10" s="15" t="inlineStr">
@@ -1470,22 +1470,22 @@
         <v>1</v>
       </c>
       <c r="K10" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33850</t>
+          <t>PDMDEP-33914</t>
         </is>
       </c>
       <c r="M10" s="15" t="inlineStr">
         <is>
-          <t>00161103</t>
+          <t>00167633</t>
         </is>
       </c>
       <c r="N10" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="16" t="n">
+        <v>2100</v>
+      </c>
+      <c r="O10" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P10" s="16" t="n">
@@ -1495,32 +1495,32 @@
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-33841</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
+          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>Commune de Nans les Pins</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Modélisation Seyne S/ Mer</t>
+          <t>MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">
@@ -1530,49 +1530,49 @@
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I11" s="12" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J11" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="L11" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33850</t>
         </is>
       </c>
       <c r="M11" s="12" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00161103</t>
         </is>
       </c>
       <c r="N11" s="13" t="n">
-        <v>657.3</v>
-      </c>
-      <c r="O11" s="17" t="n">
-        <v>219.1</v>
+        <v>0</v>
+      </c>
+      <c r="O11" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="P11" s="13" t="n">
-        <v>175.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>[CD 73)] - Purge arrêtés temporaires</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E12" s="15" t="inlineStr">
         <is>
-          <t>Purge arrêtés temporaires</t>
+          <t>Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="F12" s="15" t="inlineStr">
@@ -1614,52 +1614,52 @@
         <v>1</v>
       </c>
       <c r="K12" s="15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L12" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="M12" s="15" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="N12" s="16" t="n">
-        <v>1890</v>
+        <v>657.3</v>
       </c>
       <c r="O12" s="17" t="n">
-        <v>0</v>
+        <v>219.1</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>0</v>
+        <v>175.28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33790</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
+          <t>[CD 73)] - Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commande modélisation supplémentaire </t>
+          <t>Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
@@ -1679,29 +1679,29 @@
       </c>
       <c r="I13" s="12" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J13" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L13" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33794</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="M13" s="12" t="inlineStr">
         <is>
-          <t>00169697</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="N13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="13" t="n">
+        <v>1890</v>
+      </c>
+      <c r="O13" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P13" s="13" t="n">
@@ -1711,32 +1711,32 @@
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33755</t>
+          <t>PDMDEP-33790</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MAINTENON] - Migration vers GeoDP V2</t>
+          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>Quentin BORDILLON</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE MAINTENON</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E14" s="15" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t xml:space="preserve">Commande modélisation supplémentaire </t>
         </is>
       </c>
       <c r="F14" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G14" s="15" t="inlineStr">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="H14" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I14" s="15" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="J14" s="15" t="n">
         <v>1</v>
       </c>
       <c r="K14" s="15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L14" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33764</t>
+          <t>PDMDEP-33794</t>
         </is>
       </c>
       <c r="M14" s="15" t="inlineStr">
         <is>
-          <t>00169558</t>
+          <t>00169697</t>
         </is>
       </c>
       <c r="N14" s="16" t="n">
-        <v>1365</v>
-      </c>
-      <c r="O14" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P14" s="16" t="n">
@@ -1783,32 +1783,32 @@
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33729</t>
+          <t>PDMDEP-33755</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information] - MONTEE DE VERSION LITT EXP  test et prod </t>
+          <t>[COMMUNE DE MAINTENON] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Quentin BORDILLON</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information</t>
+          <t>COMMUNE DE MAINTENON</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MONTEE DE VERSION LITT EXP  test et prod </t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G15" s="12" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I15" s="12" t="inlineStr">
@@ -1830,22 +1830,22 @@
         <v>1</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L15" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33733</t>
+          <t>PDMDEP-33764</t>
         </is>
       </c>
       <c r="M15" s="12" t="inlineStr">
         <is>
-          <t>00169480</t>
+          <t>00169558</t>
         </is>
       </c>
       <c r="N15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="13" t="n">
+        <v>1365</v>
+      </c>
+      <c r="O15" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P15" s="13" t="n">
@@ -1855,12 +1855,12 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33720</t>
+          <t>PDMDEP-33729</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LEVALLOIS PERRET] - PRESTA PURGE DES ACTES EN URGENCE</t>
+          <t xml:space="preserve">[VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information] - MONTEE DE VERSION LITT EXP  test et prod </t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
@@ -1870,12 +1870,12 @@
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information</t>
         </is>
       </c>
       <c r="E16" s="15" t="inlineStr">
         <is>
-          <t>PRESTA PURGE DES ACTES EN URGENCE</t>
+          <t xml:space="preserve">MONTEE DE VERSION LITT EXP  test et prod </t>
         </is>
       </c>
       <c r="F16" s="15" t="inlineStr">
@@ -1902,22 +1902,22 @@
         <v>1</v>
       </c>
       <c r="K16" s="15" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L16" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33724</t>
+          <t>PDMDEP-33733</t>
         </is>
       </c>
       <c r="M16" s="15" t="inlineStr">
         <is>
-          <t>00169462</t>
+          <t>00169480</t>
         </is>
       </c>
       <c r="N16" s="16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="O16" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P16" s="16" t="n">
@@ -1927,32 +1927,32 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33686</t>
+          <t>PDMDEP-33720</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>[EUROMETROPOLE DE METZ] - Paiement CB + 3 PAX</t>
+          <t>[COMMUNE DE LEVALLOIS PERRET] - PRESTA PURGE DES ACTES EN URGENCE</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>EUROMETROPOLE DE METZ</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Paiement CB + 3 PAX</t>
+          <t>PRESTA PURGE DES ACTES EN URGENCE</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
@@ -1967,27 +1967,27 @@
       </c>
       <c r="I17" s="12" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J17" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L17" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33694</t>
+          <t>PDMDEP-33724</t>
         </is>
       </c>
       <c r="M17" s="12" t="inlineStr">
         <is>
-          <t>00169321</t>
+          <t>00169462</t>
         </is>
       </c>
       <c r="N17" s="13" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="O17" s="17" t="n">
         <v>0</v>
@@ -1999,27 +1999,27 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33610</t>
+          <t>PDMDEP-33686</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MORLAIX] - MIGRATION GEODP PLACIER hors matériel </t>
+          <t>[EUROMETROPOLE DE METZ] - Paiement CB + 3 PAX</t>
         </is>
       </c>
       <c r="C18" s="15" t="inlineStr">
         <is>
-          <t>Quentin BORDILLON</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D18" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE MORLAIX</t>
+          <t>EUROMETROPOLE DE METZ</t>
         </is>
       </c>
       <c r="E18" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
+          <t>Paiement CB + 3 PAX</t>
         </is>
       </c>
       <c r="F18" s="15" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="H18" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I18" s="15" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="J18" s="15" t="n">
@@ -2050,16 +2050,16 @@
       </c>
       <c r="L18" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33616</t>
+          <t>PDMDEP-33694</t>
         </is>
       </c>
       <c r="M18" s="15" t="inlineStr">
         <is>
-          <t>00169015</t>
+          <t>00169321</t>
         </is>
       </c>
       <c r="N18" s="16" t="n">
-        <v>4040</v>
+        <v>1500</v>
       </c>
       <c r="O18" s="17" t="n">
         <v>0</v>
@@ -2071,32 +2071,32 @@
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33566</t>
+          <t>PDMDEP-33610</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LILLE] Flux WFS</t>
+          <t xml:space="preserve">[COMMUNE DE MORLAIX] - MIGRATION GEODP PLACIER hors matériel </t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Quentin BORDILLON</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE LILLE</t>
+          <t>COMMUNE DE MORLAIX</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>MM - Up - LiExp - Flux WFS (PS)</t>
+          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G19" s="12" t="inlineStr">
@@ -2106,12 +2106,12 @@
       </c>
       <c r="H19" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I19" s="12" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J19" s="12" t="n">
@@ -2122,16 +2122,16 @@
       </c>
       <c r="L19" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33570</t>
+          <t>PDMDEP-33616</t>
         </is>
       </c>
       <c r="M19" s="12" t="inlineStr">
         <is>
-          <t>00168466</t>
+          <t>00169015</t>
         </is>
       </c>
       <c r="N19" s="13" t="n">
-        <v>895</v>
+        <v>4040</v>
       </c>
       <c r="O19" s="17" t="n">
         <v>0</v>
@@ -2143,32 +2143,32 @@
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33553</t>
+          <t>PDMDEP-33566</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - MM - Up - GeODP - PAX</t>
+          <t>[COMMUNE DE LILLE] Flux WFS</t>
         </is>
       </c>
       <c r="C20" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D20" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>COMMUNE DE LILLE</t>
         </is>
       </c>
       <c r="E20" s="15" t="inlineStr">
         <is>
-          <t>MM - Up - GeODP - PAX</t>
+          <t>MM - Up - LiExp - Flux WFS (PS)</t>
         </is>
       </c>
       <c r="F20" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G20" s="15" t="inlineStr">
@@ -2194,16 +2194,16 @@
       </c>
       <c r="L20" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33561</t>
+          <t>PDMDEP-33570</t>
         </is>
       </c>
       <c r="M20" s="15" t="inlineStr">
         <is>
-          <t>00168460</t>
+          <t>00168466</t>
         </is>
       </c>
       <c r="N20" s="16" t="n">
-        <v>500</v>
+        <v>895</v>
       </c>
       <c r="O20" s="17" t="n">
         <v>0</v>
@@ -2215,32 +2215,32 @@
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33553</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - MM - Up - GeODP - PAX</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t>MM - Up - GeODP - PAX</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G21" s="12" t="inlineStr">
@@ -2255,27 +2255,27 @@
       </c>
       <c r="I21" s="12" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="J21" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33561</t>
         </is>
       </c>
       <c r="M21" s="12" t="inlineStr">
         <is>
-          <t>00168025</t>
+          <t>00168460</t>
         </is>
       </c>
       <c r="N21" s="13" t="n">
-        <v>171.4</v>
+        <v>500</v>
       </c>
       <c r="O21" s="17" t="n">
         <v>0</v>
@@ -2287,32 +2287,32 @@
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33461</t>
+          <t>PDMDEP-33471</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>[Mairie de Buis-les-baronnies] - INITIATION GEODP</t>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>Mairie de Buis-les-baronnies</t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E22" s="15" t="inlineStr">
         <is>
-          <t>INITIATION GEODP</t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="F22" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G22" s="15" t="inlineStr">
@@ -2338,16 +2338,16 @@
       </c>
       <c r="L22" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33465</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="M22" s="15" t="inlineStr">
         <is>
-          <t>00167986</t>
+          <t>00168025</t>
         </is>
       </c>
       <c r="N22" s="16" t="n">
-        <v>450</v>
+        <v>171.4</v>
       </c>
       <c r="O22" s="17" t="n">
         <v>0</v>
@@ -2359,32 +2359,32 @@
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33451</t>
+          <t>PDMDEP-33461</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>[VILLE DE CHATELLERAULT] - FDS pour Littéralis Expert</t>
+          <t>[Mairie de Buis-les-baronnies] - INITIATION GEODP</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE CHATELLERAULT</t>
+          <t>Mairie de Buis-les-baronnies</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>FDS pour Littéralis Expert</t>
+          <t>INITIATION GEODP</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G23" s="12" t="inlineStr">
@@ -2406,22 +2406,22 @@
         <v>2</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L23" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33455</t>
+          <t>PDMDEP-33465</t>
         </is>
       </c>
       <c r="M23" s="12" t="inlineStr">
         <is>
-          <t>00167958</t>
+          <t>00167986</t>
         </is>
       </c>
       <c r="N23" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" s="13" t="n">
+        <v>450</v>
+      </c>
+      <c r="O23" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P23" s="13" t="n">
@@ -2431,12 +2431,12 @@
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33386</t>
+          <t>PDMDEP-33451</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE SAINT PIERRE DE LA REUNION] - Prestation modélisation Littéralis </t>
+          <t>[VILLE DE CHATELLERAULT] - FDS pour Littéralis Expert</t>
         </is>
       </c>
       <c r="C24" s="15" t="inlineStr">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="D24" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SAINT PIERRE DE LA REUNION</t>
+          <t>VILLE DE CHATELLERAULT</t>
         </is>
       </c>
       <c r="E24" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prestation modélisation Littéralis </t>
+          <t>FDS pour Littéralis Expert</t>
         </is>
       </c>
       <c r="F24" s="15" t="inlineStr">
@@ -2471,44 +2471,44 @@
       </c>
       <c r="I24" s="15" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J24" s="15" t="n">
         <v>2</v>
       </c>
       <c r="K24" s="15" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="L24" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33390</t>
+          <t>PDMDEP-33455</t>
         </is>
       </c>
       <c r="M24" s="15" t="inlineStr">
         <is>
-          <t>00167823</t>
+          <t>00167958</t>
         </is>
       </c>
       <c r="N24" s="16" t="n">
-        <v>617.04</v>
+        <v>0</v>
       </c>
       <c r="O24" s="16" t="n">
-        <v>1028.4</v>
+        <v>0</v>
       </c>
       <c r="P24" s="16" t="n">
-        <v>1371.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33363</t>
+          <t>PDMDEP-33386</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>[AMIENS METROPOLE] LiExp - Vérif</t>
+          <t xml:space="preserve">[COMMUNE DE SAINT PIERRE DE LA REUNION] - Prestation modélisation Littéralis </t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>AMIENS METROPOLE</t>
+          <t>COMMUNE DE SAINT PIERRE DE LA REUNION</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>MM - Up - LiExp - Vérif</t>
+          <t xml:space="preserve">Prestation modélisation Littéralis </t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
@@ -2543,36 +2543,44 @@
       </c>
       <c r="I25" s="12" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J25" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L25" s="12" t="inlineStr"/>
-      <c r="M25" s="12" t="inlineStr"/>
+        <v>0.75</v>
+      </c>
+      <c r="L25" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-33390</t>
+        </is>
+      </c>
+      <c r="M25" s="12" t="inlineStr">
+        <is>
+          <t>00167823</t>
+        </is>
+      </c>
       <c r="N25" s="13" t="n">
-        <v>0</v>
+        <v>617.04</v>
       </c>
       <c r="O25" s="13" t="n">
-        <v>0</v>
+        <v>1028.4</v>
       </c>
       <c r="P25" s="13" t="n">
-        <v>0</v>
+        <v>1371.2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33348</t>
+          <t>PDMDEP-33363</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[MAISONS ALFORT] - Modélisation + Modif Marianne </t>
+          <t>[AMIENS METROPOLE] LiExp - Vérif</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
@@ -2582,12 +2590,12 @@
       </c>
       <c r="D26" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMUNE DE MAISONS ALFORT </t>
+          <t>AMIENS METROPOLE</t>
         </is>
       </c>
       <c r="E26" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modélisation + Modif Marianne </t>
+          <t>MM - Up - LiExp - Vérif</t>
         </is>
       </c>
       <c r="F26" s="15" t="inlineStr">
@@ -2597,7 +2605,7 @@
       </c>
       <c r="G26" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H26" s="15" t="inlineStr">
@@ -2607,29 +2615,21 @@
       </c>
       <c r="I26" s="15" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="J26" s="15" t="n">
         <v>2</v>
       </c>
       <c r="K26" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-33352</t>
-        </is>
-      </c>
-      <c r="M26" s="15" t="inlineStr">
-        <is>
-          <t>00167402</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L26" s="15" t="inlineStr"/>
+      <c r="M26" s="15" t="inlineStr"/>
       <c r="N26" s="16" t="n">
-        <v>171.4</v>
-      </c>
-      <c r="O26" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P26" s="16" t="n">
@@ -2639,27 +2639,27 @@
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33348</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - Crédits 21 heures (3j)</t>
+          <t xml:space="preserve">[MAISONS ALFORT] - Modélisation + Modif Marianne </t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t xml:space="preserve">COMMUNE DE MAISONS ALFORT </t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t xml:space="preserve">Modélisation + Modif Marianne </t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
@@ -2679,27 +2679,27 @@
       </c>
       <c r="I27" s="12" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="J27" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L27" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33352</t>
         </is>
       </c>
       <c r="M27" s="12" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00167402</t>
         </is>
       </c>
       <c r="N27" s="13" t="n">
-        <v>1250</v>
+        <v>171.4</v>
       </c>
       <c r="O27" s="17" t="n">
         <v>0</v>
@@ -2762,16 +2762,16 @@
       </c>
       <c r="L28" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33231</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M28" s="15" t="inlineStr">
         <is>
-          <t>00166707</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N28" s="16" t="n">
-        <v>600</v>
+        <v>1250</v>
       </c>
       <c r="O28" s="17" t="n">
         <v>0</v>
@@ -2783,32 +2783,32 @@
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33012</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - Crédits 21 heures (3j)</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE GRASSE</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Migration GeODP + Module Terrasse + formation sur site</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G29" s="12" t="inlineStr">
@@ -2818,69 +2818,69 @@
       </c>
       <c r="H29" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I29" s="12" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J29" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>3.5</v>
+        <v>0.25</v>
       </c>
       <c r="L29" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33021</t>
+          <t>PDMDEP-33231</t>
         </is>
       </c>
       <c r="M29" s="12" t="inlineStr">
         <is>
-          <t>00165368</t>
+          <t>00166707</t>
         </is>
       </c>
       <c r="N29" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="13" t="n">
-        <v>1079</v>
+        <v>600</v>
+      </c>
+      <c r="O29" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P29" s="13" t="n">
-        <v>308.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33012</t>
         </is>
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D30" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE GRASSE</t>
         </is>
       </c>
       <c r="E30" s="15" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="F30" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G30" s="15" t="inlineStr">
@@ -2890,69 +2890,69 @@
       </c>
       <c r="H30" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I30" s="15" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="J30" s="15" t="n">
         <v>3</v>
       </c>
       <c r="K30" s="15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="L30" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33021</t>
         </is>
       </c>
       <c r="M30" s="15" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00165368</t>
         </is>
       </c>
       <c r="N30" s="16" t="n">
-        <v>2000</v>
-      </c>
-      <c r="O30" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O30" s="16" t="n">
+        <v>1079</v>
       </c>
       <c r="P30" s="16" t="n">
-        <v>0</v>
+        <v>308.29</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32967</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DU PONTET</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier 2/2</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G31" s="12" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I31" s="12" t="inlineStr">
@@ -2974,22 +2974,22 @@
         <v>3</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L31" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32974</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M31" s="12" t="inlineStr">
         <is>
-          <t>00165260</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N31" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="13" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O31" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P31" s="13" t="n">
@@ -2999,27 +2999,27 @@
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32848</t>
+          <t>PDMDEP-32967</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GRENOBLE] - Modification modèles de facture</t>
+          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="C32" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE GRENOBLE</t>
+          <t>COMMUNE DU PONTET</t>
         </is>
       </c>
       <c r="E32" s="15" t="inlineStr">
         <is>
-          <t>Modification modèles de facture</t>
+          <t>Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="F32" s="15" t="inlineStr">
@@ -3034,34 +3034,34 @@
       </c>
       <c r="H32" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I32" s="15" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J32" s="15" t="n">
         <v>3</v>
       </c>
       <c r="K32" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L32" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32852</t>
+          <t>PDMDEP-32974</t>
         </is>
       </c>
       <c r="M32" s="15" t="inlineStr">
         <is>
-          <t>00164564</t>
+          <t>00165260</t>
         </is>
       </c>
       <c r="N32" s="16" t="n">
-        <v>300</v>
-      </c>
-      <c r="O32" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P32" s="16" t="n">
@@ -3071,12 +3071,12 @@
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32831</t>
+          <t>PDMDEP-32848</t>
         </is>
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE PANTIN] - Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
+          <t>[COMMUNE DE GRENOBLE] - Modification modèles de facture</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
@@ -3086,12 +3086,12 @@
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE PANTIN</t>
+          <t>COMMUNE DE GRENOBLE</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
+          <t>Modification modèles de facture</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="I33" s="12" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="J33" s="12" t="n">
@@ -3122,16 +3122,16 @@
       </c>
       <c r="L33" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32837</t>
+          <t>PDMDEP-32852</t>
         </is>
       </c>
       <c r="M33" s="12" t="inlineStr">
         <is>
-          <t>00164275</t>
+          <t>00164564</t>
         </is>
       </c>
       <c r="N33" s="13" t="n">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="O33" s="17" t="n">
         <v>0</v>
@@ -3143,32 +3143,32 @@
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32768</t>
+          <t>PDMDEP-32831</t>
         </is>
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
+          <t>[COMMUNE DE PANTIN] - Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
         </is>
       </c>
       <c r="C34" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D34" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE REIMS</t>
+          <t>COMMUNE DE PANTIN</t>
         </is>
       </c>
       <c r="E34" s="15" t="inlineStr">
         <is>
-          <t>MV app/ infra + màj carto</t>
+          <t>Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
         </is>
       </c>
       <c r="F34" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G34" s="15" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="I34" s="15" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="J34" s="15" t="n">
@@ -3194,16 +3194,16 @@
       </c>
       <c r="L34" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32772</t>
+          <t>PDMDEP-32837</t>
         </is>
       </c>
       <c r="M34" s="15" t="inlineStr">
         <is>
-          <t>00163806</t>
+          <t>00164275</t>
         </is>
       </c>
       <c r="N34" s="16" t="n">
-        <v>705</v>
+        <v>900</v>
       </c>
       <c r="O34" s="17" t="n">
         <v>0</v>
@@ -3215,12 +3215,12 @@
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32759</t>
+          <t>PDMDEP-32768</t>
         </is>
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE DU GRAND REIMS - DSIT] - MV app/ infra + màj carto</t>
+          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE DU GRAND REIMS - DSIT</t>
+          <t>VILLE DE REIMS</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
@@ -3266,16 +3266,16 @@
       </c>
       <c r="L35" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32763</t>
+          <t>PDMDEP-32772</t>
         </is>
       </c>
       <c r="M35" s="12" t="inlineStr">
         <is>
-          <t>00163805</t>
+          <t>00163806</t>
         </is>
       </c>
       <c r="N35" s="13" t="n">
-        <v>564</v>
+        <v>705</v>
       </c>
       <c r="O35" s="17" t="n">
         <v>0</v>
@@ -3287,32 +3287,32 @@
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32732</t>
+          <t>PDMDEP-32759</t>
         </is>
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
+          <t>[COMMUNAUTE URBAINE DU GRAND REIMS - DSIT] - MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="C36" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D36" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE LA SENTINELLE</t>
+          <t>COMMUNAUTE URBAINE DU GRAND REIMS - DSIT</t>
         </is>
       </c>
       <c r="E36" s="15" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Caisse</t>
+          <t>MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="F36" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G36" s="15" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="H36" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I36" s="15" t="inlineStr">
@@ -3338,16 +3338,16 @@
       </c>
       <c r="L36" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32741</t>
+          <t>PDMDEP-32763</t>
         </is>
       </c>
       <c r="M36" s="15" t="inlineStr">
         <is>
-          <t>00163789</t>
+          <t>00163805</t>
         </is>
       </c>
       <c r="N36" s="16" t="n">
-        <v>2138.2</v>
+        <v>564</v>
       </c>
       <c r="O36" s="17" t="n">
         <v>0</v>
@@ -3359,12 +3359,12 @@
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32703</t>
+          <t>PDMDEP-32732</t>
         </is>
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[MAIRIE DE MIRIBEL] - MIGRATION PLACIER SIMPLE + PAX </t>
+          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE MIRIBEL</t>
+          <t>MAIRIE DE LA SENTINELLE</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGRATION PLACIER SIMPLE + PAX </t>
+          <t>Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
@@ -3394,12 +3394,12 @@
       </c>
       <c r="H37" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I37" s="12" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J37" s="12" t="n">
@@ -3410,16 +3410,16 @@
       </c>
       <c r="L37" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32712</t>
+          <t>PDMDEP-32741</t>
         </is>
       </c>
       <c r="M37" s="12" t="inlineStr">
         <is>
-          <t>00163498</t>
+          <t>00163789</t>
         </is>
       </c>
       <c r="N37" s="13" t="n">
-        <v>283.5</v>
+        <v>2138.2</v>
       </c>
       <c r="O37" s="17" t="n">
         <v>0</v>
@@ -3431,32 +3431,32 @@
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32625</t>
+          <t>PDMDEP-32703</t>
         </is>
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Modélisation LiEx</t>
+          <t xml:space="preserve">[MAIRIE DE MIRIBEL] - MIGRATION PLACIER SIMPLE + PAX </t>
         </is>
       </c>
       <c r="C38" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D38" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANTIBES</t>
+          <t>MAIRIE DE MIRIBEL</t>
         </is>
       </c>
       <c r="E38" s="15" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t xml:space="preserve">MIGRATION PLACIER SIMPLE + PAX </t>
         </is>
       </c>
       <c r="F38" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G38" s="15" t="inlineStr">
@@ -3466,32 +3466,32 @@
       </c>
       <c r="H38" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I38" s="15" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="J38" s="15" t="n">
         <v>3</v>
       </c>
       <c r="K38" s="15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L38" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32629</t>
+          <t>PDMDEP-32712</t>
         </is>
       </c>
       <c r="M38" s="15" t="inlineStr">
         <is>
-          <t>00163182</t>
+          <t>00163498</t>
         </is>
       </c>
       <c r="N38" s="16" t="n">
-        <v>548.4</v>
+        <v>283.5</v>
       </c>
       <c r="O38" s="17" t="n">
         <v>0</v>
@@ -3503,32 +3503,32 @@
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32598</t>
+          <t>PDMDEP-32625</t>
         </is>
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
+          <t>[ANTIBES] - Modélisation LiEx</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>Déploiement GeoDP Caisse</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G39" s="12" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H39" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I39" s="12" t="inlineStr">
@@ -3550,20 +3550,20 @@
         <v>3</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L39" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32607</t>
+          <t>PDMDEP-32629</t>
         </is>
       </c>
       <c r="M39" s="12" t="inlineStr">
         <is>
-          <t>00163155</t>
+          <t>00163182</t>
         </is>
       </c>
       <c r="N39" s="13" t="n">
-        <v>552</v>
+        <v>548.4</v>
       </c>
       <c r="O39" s="17" t="n">
         <v>0</v>
@@ -3575,32 +3575,32 @@
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32598</t>
         </is>
       </c>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="C40" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D40" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
         </is>
       </c>
       <c r="E40" s="15" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="F40" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G40" s="15" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="H40" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I40" s="15" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J40" s="15" t="n">
@@ -3626,16 +3626,16 @@
       </c>
       <c r="L40" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32607</t>
         </is>
       </c>
       <c r="M40" s="15" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00163155</t>
         </is>
       </c>
       <c r="N40" s="16" t="n">
-        <v>142.1</v>
+        <v>552</v>
       </c>
       <c r="O40" s="17" t="n">
         <v>0</v>
@@ -3647,32 +3647,32 @@
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G41" s="12" t="inlineStr">
@@ -3682,32 +3682,32 @@
       </c>
       <c r="H41" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I41" s="12" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J41" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L41" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M41" s="12" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N41" s="13" t="n">
-        <v>1868</v>
+        <v>142.1</v>
       </c>
       <c r="O41" s="17" t="n">
         <v>0</v>
@@ -3719,32 +3719,32 @@
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32442</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod </t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C42" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D42" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E42" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F42" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G42" s="15" t="inlineStr">
@@ -3754,32 +3754,32 @@
       </c>
       <c r="H42" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I42" s="15" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J42" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K42" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L42" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32446</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M42" s="15" t="inlineStr">
         <is>
-          <t>00161842</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N42" s="16" t="n">
-        <v>882.5</v>
+        <v>1868</v>
       </c>
       <c r="O42" s="17" t="n">
         <v>0</v>
@@ -3791,27 +3791,27 @@
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32400</t>
+          <t>PDMDEP-32442</t>
         </is>
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>[SM GESTION DES ROUTES DE GUADELOUPE] - Littéralis Expert - Interface Parapheur Ixbus</t>
+          <t xml:space="preserve">[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>SM GESTION DES ROUTES DE GUADELOUPE</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>Littéralis Expert - Interface Parapheur Ixbus</t>
+          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="F43" s="12" t="inlineStr">
@@ -3831,29 +3831,29 @@
       </c>
       <c r="I43" s="12" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="J43" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32406</t>
+          <t>PDMDEP-32446</t>
         </is>
       </c>
       <c r="M43" s="12" t="inlineStr">
         <is>
-          <t>00161680</t>
+          <t>00161842</t>
         </is>
       </c>
       <c r="N43" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" s="13" t="n">
+        <v>882.5</v>
+      </c>
+      <c r="O43" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P43" s="13" t="n">
@@ -3863,32 +3863,32 @@
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32400</t>
         </is>
       </c>
       <c r="B44" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[SM GESTION DES ROUTES DE GUADELOUPE] - Littéralis Expert - Interface Parapheur Ixbus</t>
         </is>
       </c>
       <c r="C44" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D44" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>SM GESTION DES ROUTES DE GUADELOUPE</t>
         </is>
       </c>
       <c r="E44" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Littéralis Expert - Interface Parapheur Ixbus</t>
         </is>
       </c>
       <c r="F44" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G44" s="15" t="inlineStr">
@@ -3898,34 +3898,34 @@
       </c>
       <c r="H44" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I44" s="15" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="J44" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K44" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32406</t>
         </is>
       </c>
       <c r="M44" s="15" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161680</t>
         </is>
       </c>
       <c r="N44" s="16" t="n">
-        <v>450</v>
-      </c>
-      <c r="O44" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P44" s="16" t="n">
@@ -3935,32 +3935,32 @@
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F45" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G45" s="12" t="inlineStr">
@@ -3970,32 +3970,32 @@
       </c>
       <c r="H45" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I45" s="12" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J45" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L45" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M45" s="12" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N45" s="13" t="n">
-        <v>1046.5</v>
+        <v>450</v>
       </c>
       <c r="O45" s="17" t="n">
         <v>0</v>
@@ -4007,32 +4007,32 @@
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32121</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C46" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D46" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARAN</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E46" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE + Exp Ciril</t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F46" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G46" s="15" t="inlineStr">
@@ -4042,32 +4042,32 @@
       </c>
       <c r="H46" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I46" s="15" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J46" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K46" s="15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L46" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32128</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M46" s="15" t="inlineStr">
         <is>
-          <t>00160621</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N46" s="16" t="n">
-        <v>250</v>
+        <v>1046.5</v>
       </c>
       <c r="O46" s="17" t="n">
         <v>0</v>
@@ -4079,27 +4079,27 @@
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F47" s="12" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="H47" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I47" s="12" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J47" s="12" t="n">
@@ -4130,16 +4130,16 @@
       </c>
       <c r="L47" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M47" s="12" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N47" s="13" t="n">
-        <v>407</v>
+        <v>250</v>
       </c>
       <c r="O47" s="17" t="n">
         <v>0</v>
@@ -4151,32 +4151,32 @@
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C48" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D48" s="15" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E48" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F48" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G48" s="15" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="I48" s="15" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J48" s="15" t="n">
@@ -4202,16 +4202,16 @@
       </c>
       <c r="L48" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M48" s="15" t="inlineStr">
         <is>
-          <t>00160148</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N48" s="16" t="n">
-        <v>440.38</v>
+        <v>407</v>
       </c>
       <c r="O48" s="17" t="n">
         <v>0</v>
@@ -4223,32 +4223,32 @@
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F49" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G49" s="12" t="inlineStr">
@@ -4258,12 +4258,12 @@
       </c>
       <c r="H49" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I49" s="12" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J49" s="12" t="n">
@@ -4274,16 +4274,16 @@
       </c>
       <c r="L49" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M49" s="12" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N49" s="13" t="n">
-        <v>285</v>
+        <v>440.38</v>
       </c>
       <c r="O49" s="17" t="n">
         <v>0</v>
@@ -4295,32 +4295,32 @@
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C50" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D50" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E50" s="15" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F50" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G50" s="15" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="I50" s="15" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J50" s="15" t="n">
@@ -4346,16 +4346,16 @@
       </c>
       <c r="L50" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M50" s="15" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N50" s="16" t="n">
-        <v>2650</v>
+        <v>285</v>
       </c>
       <c r="O50" s="17" t="n">
         <v>0</v>
@@ -4367,12 +4367,12 @@
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F51" s="12" t="inlineStr">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="I51" s="12" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J51" s="12" t="n">
@@ -4418,16 +4418,16 @@
       </c>
       <c r="L51" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M51" s="12" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N51" s="13" t="n">
-        <v>120</v>
+        <v>2650</v>
       </c>
       <c r="O51" s="17" t="n">
         <v>0</v>
@@ -4439,32 +4439,32 @@
     <row r="52">
       <c r="A52" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C52" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D52" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E52" s="15" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F52" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G52" s="15" t="inlineStr">
@@ -4474,35 +4474,35 @@
       </c>
       <c r="H52" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I52" s="15" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J52" s="15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K52" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L52" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M52" s="15" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N52" s="16" t="n">
-        <v>203.5</v>
-      </c>
-      <c r="O52" s="17" t="n">
-        <v>0</v>
+        <v>120</v>
+      </c>
+      <c r="O52" s="16" t="n">
+        <v>120</v>
       </c>
       <c r="P52" s="16" t="n">
         <v>0</v>
@@ -4511,12 +4511,12 @@
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F53" s="12" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="H53" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I53" s="12" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J53" s="12" t="n">
@@ -4562,16 +4562,16 @@
       </c>
       <c r="L53" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M53" s="12" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N53" s="13" t="n">
-        <v>150</v>
+        <v>203.5</v>
       </c>
       <c r="O53" s="17" t="n">
         <v>0</v>
@@ -4583,32 +4583,32 @@
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B54" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C54" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D54" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E54" s="15" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F54" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G54" s="15" t="inlineStr">
@@ -4618,32 +4618,32 @@
       </c>
       <c r="H54" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I54" s="15" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J54" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K54" s="15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L54" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31596</t>
         </is>
       </c>
       <c r="M54" s="15" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00157967</t>
         </is>
       </c>
       <c r="N54" s="16" t="n">
-        <v>3288.55</v>
+        <v>150</v>
       </c>
       <c r="O54" s="17" t="n">
         <v>0</v>
@@ -4655,27 +4655,27 @@
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31516</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>[VIRE NORMANDIE] - Litteralis Verif</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIRE NORMANDIE</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>Litteralis Verif</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F55" s="12" t="inlineStr">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H55" s="12" t="inlineStr">
@@ -4702,14 +4702,22 @@
         <v>5</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L55" s="12" t="inlineStr"/>
-      <c r="M55" s="12" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L55" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-31546</t>
+        </is>
+      </c>
+      <c r="M55" s="12" t="inlineStr">
+        <is>
+          <t>00157816</t>
+        </is>
+      </c>
       <c r="N55" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" s="13" t="n">
+        <v>3288.55</v>
+      </c>
+      <c r="O55" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P55" s="13" t="n">
@@ -4719,12 +4727,12 @@
     <row r="56">
       <c r="A56" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31464</t>
+          <t>PDMDEP-31516</t>
         </is>
       </c>
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t>[CD 17] - Modélisation PV - 2 jours</t>
+          <t>[VIRE NORMANDIE] - Litteralis Verif</t>
         </is>
       </c>
       <c r="C56" s="15" t="inlineStr">
@@ -4734,12 +4742,12 @@
       </c>
       <c r="D56" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>COMMUNE DE VIRE NORMANDIE</t>
         </is>
       </c>
       <c r="E56" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
+          <t>Litteralis Verif</t>
         </is>
       </c>
       <c r="F56" s="15" t="inlineStr">
@@ -4749,7 +4757,7 @@
       </c>
       <c r="G56" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H56" s="15" t="inlineStr">
@@ -4759,25 +4767,17 @@
       </c>
       <c r="I56" s="15" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J56" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K56" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L56" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-31468</t>
-        </is>
-      </c>
-      <c r="M56" s="15" t="inlineStr">
-        <is>
-          <t>00157346</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L56" s="15" t="inlineStr"/>
+      <c r="M56" s="15" t="inlineStr"/>
       <c r="N56" s="16" t="n">
         <v>0</v>
       </c>
@@ -4791,32 +4791,32 @@
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31464</t>
         </is>
       </c>
       <c r="B57" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[CD 17] - Modélisation PV - 2 jours</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
         </is>
       </c>
       <c r="F57" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G57" s="12" t="inlineStr">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="H57" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I57" s="12" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="J57" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L57" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31468</t>
         </is>
       </c>
       <c r="M57" s="12" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157346</t>
         </is>
       </c>
       <c r="N57" s="13" t="n">
-        <v>210</v>
-      </c>
-      <c r="O57" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P57" s="13" t="n">
@@ -4863,32 +4863,32 @@
     <row r="58">
       <c r="A58" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31285</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LUNEL] - FDS pour Littéralis Expert. Déjà chiffré en amont dans le ticket 1333</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C58" s="15" t="inlineStr">
         <is>
-          <t>Valentin CAUJOLLE</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D58" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LUNEL</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E58" s="15" t="inlineStr">
         <is>
-          <t>FDS pour Littéralis Expert. Déjà chiffré en amont dans le ticket 1333</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F58" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G58" s="15" t="inlineStr">
@@ -4898,12 +4898,12 @@
       </c>
       <c r="H58" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I58" s="15" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J58" s="15" t="n">
@@ -4914,16 +4914,16 @@
       </c>
       <c r="L58" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31289</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M58" s="15" t="inlineStr">
         <is>
-          <t>00156834</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N58" s="16" t="n">
-        <v>71.2</v>
+        <v>210</v>
       </c>
       <c r="O58" s="17" t="n">
         <v>0</v>
@@ -4935,32 +4935,32 @@
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31285</t>
         </is>
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE LUNEL] - FDS pour Littéralis Expert. Déjà chiffré en amont dans le ticket 1333</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Valentin CAUJOLLE</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE LUNEL</t>
         </is>
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>FDS pour Littéralis Expert. Déjà chiffré en amont dans le ticket 1333</t>
         </is>
       </c>
       <c r="F59" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G59" s="12" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="H59" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I59" s="12" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>16/02/2026</t>
         </is>
       </c>
       <c r="J59" s="12" t="n">
@@ -4986,16 +4986,16 @@
       </c>
       <c r="L59" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31289</t>
         </is>
       </c>
       <c r="M59" s="12" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00156834</t>
         </is>
       </c>
       <c r="N59" s="13" t="n">
-        <v>130</v>
+        <v>71.2</v>
       </c>
       <c r="O59" s="17" t="n">
         <v>0</v>
@@ -5007,12 +5007,12 @@
     <row r="60">
       <c r="A60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C60" s="15" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="D60" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E60" s="15" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F60" s="15" t="inlineStr">
@@ -5047,7 +5047,7 @@
       </c>
       <c r="I60" s="15" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J60" s="15" t="n">
@@ -5058,16 +5058,16 @@
       </c>
       <c r="L60" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M60" s="15" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N60" s="16" t="n">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="O60" s="17" t="n">
         <v>0</v>
@@ -5079,12 +5079,12 @@
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30358</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
@@ -5094,12 +5094,12 @@
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARGELES-SUR-MER</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F61" s="12" t="inlineStr">
@@ -5119,27 +5119,27 @@
       </c>
       <c r="I61" s="12" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J61" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K61" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L61" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30366</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M61" s="12" t="inlineStr">
         <is>
-          <t>00154569</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N61" s="13" t="n">
-        <v>1000</v>
+        <v>255</v>
       </c>
       <c r="O61" s="17" t="n">
         <v>0</v>
@@ -5151,12 +5151,12 @@
     <row r="62">
       <c r="A62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-30358</t>
         </is>
       </c>
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C62" s="15" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="D62" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE D'ARGELES-SUR-MER</t>
         </is>
       </c>
       <c r="E62" s="15" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F62" s="15" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="I62" s="15" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="J62" s="15" t="n">
@@ -5202,16 +5202,16 @@
       </c>
       <c r="L62" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-30366</t>
         </is>
       </c>
       <c r="M62" s="15" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00154569</t>
         </is>
       </c>
       <c r="N62" s="16" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="O62" s="17" t="n">
         <v>0</v>
@@ -5223,27 +5223,27 @@
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30311</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CAEN] - GeODP - Modification des marges via activation Editique</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAEN</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>GeODP - Modification des marges via activation Editique</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F63" s="12" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="I63" s="12" t="inlineStr">
         <is>
-          <t>27/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J63" s="12" t="n">
@@ -5274,16 +5274,16 @@
       </c>
       <c r="L63" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30316</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M63" s="12" t="inlineStr">
         <is>
-          <t>00154362</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N63" s="13" t="n">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="O63" s="17" t="n">
         <v>0</v>
@@ -5295,32 +5295,32 @@
     <row r="64">
       <c r="A64" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30311</t>
         </is>
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE CAEN] - GeODP - Modification des marges via activation Editique</t>
         </is>
       </c>
       <c r="C64" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D64" s="15" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE CAEN</t>
         </is>
       </c>
       <c r="E64" s="15" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>GeODP - Modification des marges via activation Editique</t>
         </is>
       </c>
       <c r="F64" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G64" s="15" t="inlineStr">
@@ -5330,34 +5330,34 @@
       </c>
       <c r="H64" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I64" s="15" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>27/01/2026</t>
         </is>
       </c>
       <c r="J64" s="15" t="n">
         <v>6</v>
       </c>
       <c r="K64" s="15" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L64" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30316</t>
         </is>
       </c>
       <c r="M64" s="15" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00154362</t>
         </is>
       </c>
       <c r="N64" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" s="16" t="n">
+        <v>200</v>
+      </c>
+      <c r="O64" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P64" s="16" t="n">
@@ -5367,12 +5367,12 @@
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30062</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t>[Commune de Saint-Dizier] - Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>Commune de Saint-Dizier</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F65" s="12" t="inlineStr">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="I65" s="12" t="inlineStr">
         <is>
-          <t>19/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J65" s="12" t="n">
@@ -5418,18 +5418,18 @@
       </c>
       <c r="L65" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30063</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M65" s="12" t="inlineStr">
         <is>
-          <t>00153633</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N65" s="13" t="n">
-        <v>350</v>
-      </c>
-      <c r="O65" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P65" s="13" t="n">
@@ -5439,27 +5439,27 @@
     <row r="66">
       <c r="A66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29948</t>
+          <t>PDMDEP-30062</t>
         </is>
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
+          <t>[Commune de Saint-Dizier] - Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
         </is>
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D66" s="15" t="inlineStr">
         <is>
-          <t>MAIRE DE PONTARLIER</t>
+          <t>Commune de Saint-Dizier</t>
         </is>
       </c>
       <c r="E66" s="15" t="inlineStr">
         <is>
-          <t>Projet d'options supplémentaires Littéralis Expert</t>
+          <t>Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
         </is>
       </c>
       <c r="F66" s="15" t="inlineStr">
@@ -5479,29 +5479,29 @@
       </c>
       <c r="I66" s="15" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>19/01/2026</t>
         </is>
       </c>
       <c r="J66" s="15" t="n">
         <v>6</v>
       </c>
       <c r="K66" s="15" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="L66" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29949</t>
+          <t>PDMDEP-30063</t>
         </is>
       </c>
       <c r="M66" s="15" t="inlineStr">
         <is>
-          <t>00152726</t>
+          <t>00153633</t>
         </is>
       </c>
       <c r="N66" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" s="16" t="n">
+        <v>350</v>
+      </c>
+      <c r="O66" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P66" s="16" t="n">
@@ -5511,12 +5511,12 @@
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-29948</t>
         </is>
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
@@ -5526,12 +5526,12 @@
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>MAIRE DE PONTARLIER</t>
         </is>
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Projet d'options supplémentaires Littéralis Expert</t>
         </is>
       </c>
       <c r="F67" s="12" t="inlineStr">
@@ -5551,23 +5551,23 @@
       </c>
       <c r="I67" s="12" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J67" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>0.08</v>
+        <v>1.5</v>
       </c>
       <c r="L67" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30431</t>
+          <t>PDMDEP-29949</t>
         </is>
       </c>
       <c r="M67" s="12" t="inlineStr">
         <is>
-          <t>00154684</t>
+          <t>00152726</t>
         </is>
       </c>
       <c r="N67" s="13" t="n">
@@ -5634,12 +5634,12 @@
       </c>
       <c r="L68" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-30431</t>
         </is>
       </c>
       <c r="M68" s="15" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00154684</t>
         </is>
       </c>
       <c r="N68" s="16" t="n">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="L69" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M69" s="12" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N69" s="13" t="n">
@@ -5727,26 +5727,28 @@
     <row r="70">
       <c r="A70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29122</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DES DEUX SEVRES (CD 79) - LITTERALIS - Flux WFS communication</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D70" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DES DEUX SEVRES (CD 79)</t>
-        </is>
-      </c>
-      <c r="E70" s="15" t="n">
-        <v/>
+          <t>COMMUNE DE BIARRITZ</t>
+        </is>
+      </c>
+      <c r="E70" s="15" t="inlineStr">
+        <is>
+          <t>Paramétrages complémentaires + Vision</t>
+        </is>
       </c>
       <c r="F70" s="15" t="inlineStr">
         <is>
@@ -5765,29 +5767,29 @@
       </c>
       <c r="I70" s="15" t="inlineStr">
         <is>
-          <t>19/12/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J70" s="15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K70" s="15" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="L70" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29124</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M70" s="15" t="inlineStr">
         <is>
-          <t>00148148</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N70" s="16" t="n">
-        <v>157.5</v>
-      </c>
-      <c r="O70" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P70" s="16" t="n">
@@ -5797,12 +5799,12 @@
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-29122</t>
         </is>
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>DEPARTEMENT DES DEUX SEVRES (CD 79) - LITTERALIS - Flux WFS communication</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
@@ -5812,7 +5814,7 @@
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
+          <t>DEPARTEMENT DES DEUX SEVRES (CD 79)</t>
         </is>
       </c>
       <c r="E71" s="12" t="n">
@@ -5830,32 +5832,32 @@
       </c>
       <c r="H71" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I71" s="12" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>19/12/2025</t>
         </is>
       </c>
       <c r="J71" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K71" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L71" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-29124</t>
         </is>
       </c>
       <c r="M71" s="12" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00148148</t>
         </is>
       </c>
       <c r="N71" s="13" t="n">
-        <v>2812.32</v>
+        <v>157.5</v>
       </c>
       <c r="O71" s="17" t="n">
         <v>0</v>
@@ -5867,12 +5869,12 @@
     <row r="72">
       <c r="A72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
@@ -5882,13 +5884,11 @@
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E72" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E72" s="15" t="n">
+        <v/>
       </c>
       <c r="F72" s="15" t="inlineStr">
         <is>
@@ -5907,27 +5907,27 @@
       </c>
       <c r="I72" s="15" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J72" s="15" t="n">
         <v>8</v>
       </c>
       <c r="K72" s="15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L72" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M72" s="15" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N72" s="16" t="n">
-        <v>392.5</v>
+        <v>2812.32</v>
       </c>
       <c r="O72" s="17" t="n">
         <v>0</v>
@@ -5986,20 +5986,20 @@
         <v>8</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>0.25</v>
+        <v>0.45</v>
       </c>
       <c r="L73" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M73" s="12" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N73" s="13" t="n">
-        <v>1556.25</v>
+        <v>392.5</v>
       </c>
       <c r="O73" s="17" t="n">
         <v>0</v>
@@ -6058,20 +6058,20 @@
         <v>8</v>
       </c>
       <c r="K74" s="15" t="n">
-        <v>0.25</v>
+        <v>0.45</v>
       </c>
       <c r="L74" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M74" s="15" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N74" s="16" t="n">
-        <v>1790</v>
+        <v>1556.25</v>
       </c>
       <c r="O74" s="17" t="n">
         <v>0</v>
@@ -6130,22 +6130,22 @@
         <v>8</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>0.25</v>
+        <v>0.45</v>
       </c>
       <c r="L75" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M75" s="12" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N75" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" s="13" t="n">
+        <v>1790</v>
+      </c>
+      <c r="O75" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P75" s="13" t="n">
@@ -6202,16 +6202,16 @@
         <v>8</v>
       </c>
       <c r="K76" s="15" t="n">
-        <v>0.25</v>
+        <v>0.45</v>
       </c>
       <c r="L76" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M76" s="15" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N76" s="16" t="n">
@@ -6227,12 +6227,12 @@
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27634</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
@@ -6242,11 +6242,13 @@
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
-        </is>
-      </c>
-      <c r="E77" s="12" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E77" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F77" s="12" t="inlineStr">
         <is>
@@ -6260,28 +6262,28 @@
       </c>
       <c r="H77" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I77" s="12" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J77" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="L77" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27642</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M77" s="12" t="inlineStr">
         <is>
-          <t>00143935</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N77" s="13" t="n">
@@ -6297,12 +6299,12 @@
     <row r="78">
       <c r="A78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B78" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
         </is>
       </c>
       <c r="C78" s="15" t="inlineStr">
@@ -6312,7 +6314,7 @@
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
         </is>
       </c>
       <c r="E78" s="15" t="n">
@@ -6330,34 +6332,34 @@
       </c>
       <c r="H78" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I78" s="15" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J78" s="15" t="n">
         <v>8</v>
       </c>
       <c r="K78" s="15" t="n">
-        <v>2.5</v>
+        <v>0.75</v>
       </c>
       <c r="L78" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-27642</t>
         </is>
       </c>
       <c r="M78" s="15" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>00143935</t>
         </is>
       </c>
       <c r="N78" s="16" t="n">
-        <v>732</v>
-      </c>
-      <c r="O78" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P78" s="16" t="n">
@@ -6367,28 +6369,26 @@
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-26782</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
-        </is>
-      </c>
-      <c r="E79" s="12" t="inlineStr">
-        <is>
-          <t>Déploiement LiEx</t>
-        </is>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
+        </is>
+      </c>
+      <c r="E79" s="12" t="n">
+        <v/>
       </c>
       <c r="F79" s="12" t="inlineStr">
         <is>
@@ -6407,29 +6407,29 @@
       </c>
       <c r="I79" s="12" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J79" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K79" s="12" t="n">
-        <v>0.25</v>
+        <v>2.5</v>
       </c>
       <c r="L79" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-26783</t>
+          <t>PDMDEP-27557</t>
         </is>
       </c>
       <c r="M79" s="12" t="inlineStr">
         <is>
-          <t>00142659</t>
+          <t>00144532</t>
         </is>
       </c>
       <c r="N79" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O79" s="13" t="n">
+        <v>732</v>
+      </c>
+      <c r="O79" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P79" s="13" t="n">
@@ -6439,26 +6439,28 @@
     <row r="80">
       <c r="A80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-26782</t>
         </is>
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D80" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
-        </is>
-      </c>
-      <c r="E80" s="15" t="n">
-        <v/>
+          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
+        </is>
+      </c>
+      <c r="E80" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement LiEx</t>
+        </is>
       </c>
       <c r="F80" s="15" t="inlineStr">
         <is>
@@ -6477,29 +6479,29 @@
       </c>
       <c r="I80" s="15" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="J80" s="15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K80" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L80" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-26783</t>
         </is>
       </c>
       <c r="M80" s="15" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00142659</t>
         </is>
       </c>
       <c r="N80" s="16" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O80" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P80" s="16" t="n">
@@ -6509,22 +6511,22 @@
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-24426</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>[DRANCY] - Migration STD vers Exp</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE DRANCY</t>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
         </is>
       </c>
       <c r="E81" s="12" t="n">
@@ -6542,34 +6544,34 @@
       </c>
       <c r="H81" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I81" s="12" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J81" s="12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K81" s="12" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L81" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27028</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M81" s="12" t="inlineStr">
         <is>
-          <t>500950</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N81" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" s="13" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O81" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P81" s="13" t="n">
@@ -6579,22 +6581,22 @@
     <row r="82">
       <c r="A82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-24765</t>
         </is>
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>[COLOMBES] -  Litteralis - Interface Pastell</t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D82" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
+          <t>VILLE DE COLOMBES - DSIO</t>
         </is>
       </c>
       <c r="E82" s="15" t="n">
@@ -6612,28 +6614,28 @@
       </c>
       <c r="H82" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I82" s="15" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="J82" s="15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K82" s="15" t="n">
-        <v>0.12</v>
+        <v>0.25</v>
       </c>
       <c r="L82" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27996</t>
+          <t>PDMDEP-28062</t>
         </is>
       </c>
       <c r="M82" s="15" t="inlineStr">
         <is>
-          <t>501219</t>
+          <t>500768</t>
         </is>
       </c>
       <c r="N82" s="16" t="n">
@@ -6649,12 +6651,12 @@
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-24426</t>
         </is>
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>[DRANCY] - Migration STD vers Exp</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
@@ -6664,7 +6666,7 @@
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
+          <t>VILLE DE DRANCY</t>
         </is>
       </c>
       <c r="E83" s="12" t="n">
@@ -6682,28 +6684,28 @@
       </c>
       <c r="H83" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I83" s="12" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="J83" s="12" t="n">
         <v>10</v>
       </c>
       <c r="K83" s="12" t="n">
-        <v>0.12</v>
+        <v>0.25</v>
       </c>
       <c r="L83" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27995</t>
+          <t>PDMDEP-27028</t>
         </is>
       </c>
       <c r="M83" s="12" t="inlineStr">
         <is>
-          <t>501218</t>
+          <t>500950</t>
         </is>
       </c>
       <c r="N83" s="13" t="n">
@@ -6719,22 +6721,22 @@
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D84" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E84" s="15" t="n">
@@ -6757,29 +6759,29 @@
       </c>
       <c r="I84" s="15" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J84" s="15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K84" s="15" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="L84" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27996</t>
         </is>
       </c>
       <c r="M84" s="15" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>501219</t>
         </is>
       </c>
       <c r="N84" s="16" t="n">
-        <v>2323</v>
-      </c>
-      <c r="O84" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P84" s="16" t="n">
@@ -6789,22 +6791,22 @@
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-23484</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON- AJOUT LIEU DE NAISSANCE DANS FILIEN</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E85" s="12" t="n">
@@ -6812,7 +6814,7 @@
       </c>
       <c r="F85" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G85" s="12" t="inlineStr">
@@ -6822,34 +6824,34 @@
       </c>
       <c r="H85" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I85" s="12" t="inlineStr">
         <is>
-          <t>25/07/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J85" s="12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K85" s="12" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="L85" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27494</t>
+          <t>PDMDEP-27995</t>
         </is>
       </c>
       <c r="M85" s="12" t="inlineStr">
         <is>
-          <t>495695</t>
+          <t>501218</t>
         </is>
       </c>
       <c r="N85" s="13" t="n">
-        <v>140.4</v>
-      </c>
-      <c r="O85" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P85" s="13" t="n">
@@ -6859,22 +6861,22 @@
     <row r="86">
       <c r="A86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-22996</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C86" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D86" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E86" s="15" t="n">
@@ -6892,34 +6894,34 @@
       </c>
       <c r="H86" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I86" s="15" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J86" s="15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K86" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L86" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28051</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M86" s="15" t="inlineStr">
         <is>
-          <t>487190</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N86" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O86" s="16" t="n">
+        <v>2323</v>
+      </c>
+      <c r="O86" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P86" s="16" t="n">
@@ -6929,12 +6931,12 @@
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21546</t>
+          <t>PDMDEP-23484</t>
         </is>
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>[Villeurbanne] Evolution produit - impression des tickets d'infraction et de présence</t>
+          <t>METROPOLE TOULON- AJOUT LIEU DE NAISSANCE DANS FILIEN</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
@@ -6944,7 +6946,7 @@
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>VILLEURBANNE</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E87" s="12" t="n">
@@ -6967,27 +6969,27 @@
       </c>
       <c r="I87" s="12" t="inlineStr">
         <is>
-          <t>05/05/2025</t>
+          <t>25/07/2025</t>
         </is>
       </c>
       <c r="J87" s="12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K87" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L87" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28038</t>
+          <t>PDMDEP-27494</t>
         </is>
       </c>
       <c r="M87" s="12" t="inlineStr">
         <is>
-          <t>478867</t>
+          <t>495695</t>
         </is>
       </c>
       <c r="N87" s="13" t="n">
-        <v>1413.6</v>
+        <v>140.4</v>
       </c>
       <c r="O87" s="17" t="n">
         <v>0</v>
@@ -6999,22 +7001,22 @@
     <row r="88">
       <c r="A88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-22996</t>
         </is>
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
         </is>
       </c>
       <c r="C88" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D88" s="15" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E88" s="15" t="n">
@@ -7037,29 +7039,29 @@
       </c>
       <c r="I88" s="15" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>07/07/2025</t>
         </is>
       </c>
       <c r="J88" s="15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K88" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L88" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-28051</t>
         </is>
       </c>
       <c r="M88" s="15" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>487190</t>
         </is>
       </c>
       <c r="N88" s="16" t="n">
-        <v>250</v>
-      </c>
-      <c r="O88" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P88" s="16" t="n">
@@ -7069,22 +7071,22 @@
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21546</t>
         </is>
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Villeurbanne] Evolution produit - impression des tickets d'infraction et de présence</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>VILLEURBANNE</t>
         </is>
       </c>
       <c r="E89" s="12" t="n">
@@ -7092,7 +7094,7 @@
       </c>
       <c r="F89" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G89" s="12" t="inlineStr">
@@ -7107,27 +7109,27 @@
       </c>
       <c r="I89" s="12" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>05/05/2025</t>
         </is>
       </c>
       <c r="J89" s="12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K89" s="12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L89" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28038</t>
         </is>
       </c>
       <c r="M89" s="12" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>478867</t>
         </is>
       </c>
       <c r="N89" s="13" t="n">
-        <v>460</v>
+        <v>1413.6</v>
       </c>
       <c r="O89" s="17" t="n">
         <v>0</v>
@@ -7139,22 +7141,22 @@
     <row r="90">
       <c r="A90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D90" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E90" s="15" t="n">
@@ -7177,29 +7179,29 @@
       </c>
       <c r="I90" s="15" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J90" s="15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K90" s="15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L90" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27568</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M90" s="15" t="inlineStr">
         <is>
-          <t>471958</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N90" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O90" s="16" t="n">
+        <v>250</v>
+      </c>
+      <c r="O90" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P90" s="16" t="n">
@@ -7209,12 +7211,12 @@
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-19792</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
@@ -7224,7 +7226,7 @@
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E91" s="12" t="n">
@@ -7242,34 +7244,34 @@
       </c>
       <c r="H91" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I91" s="12" t="inlineStr">
         <is>
-          <t>06/03/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J91" s="12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K91" s="12" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="L91" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27377</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M91" s="12" t="inlineStr">
         <is>
-          <t>478048</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N91" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O91" s="13" t="n">
+        <v>460</v>
+      </c>
+      <c r="O91" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P91" s="13" t="n">
@@ -7279,12 +7281,12 @@
     <row r="92">
       <c r="A92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19385</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr">
@@ -7294,7 +7296,7 @@
       </c>
       <c r="D92" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARCUEIL</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E92" s="15" t="n">
@@ -7312,28 +7314,28 @@
       </c>
       <c r="H92" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I92" s="15" t="inlineStr">
         <is>
-          <t>24/02/2025</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J92" s="15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K92" s="15" t="n">
         <v>0.25</v>
       </c>
       <c r="L92" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27535</t>
+          <t>PDMDEP-27568</t>
         </is>
       </c>
       <c r="M92" s="15" t="inlineStr">
         <is>
-          <t>465345</t>
+          <t>471958</t>
         </is>
       </c>
       <c r="N92" s="16" t="n">
@@ -7349,12 +7351,12 @@
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-19792</t>
         </is>
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
@@ -7364,7 +7366,7 @@
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>VIENNE CONDRIEU AGGLOMERATION</t>
         </is>
       </c>
       <c r="E93" s="12" t="n">
@@ -7377,7 +7379,7 @@
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H93" s="12" t="inlineStr">
@@ -7387,17 +7389,25 @@
       </c>
       <c r="I93" s="12" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>06/03/2025</t>
         </is>
       </c>
       <c r="J93" s="12" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K93" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L93" s="12" t="inlineStr"/>
-      <c r="M93" s="12" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L93" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-27377</t>
+        </is>
+      </c>
+      <c r="M93" s="12" t="inlineStr">
+        <is>
+          <t>478048</t>
+        </is>
+      </c>
       <c r="N93" s="13" t="n">
         <v>0</v>
       </c>
@@ -7411,22 +7421,22 @@
     <row r="94">
       <c r="A94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-19385</t>
         </is>
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D94" s="15" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>COMMUNE D'ARCUEIL</t>
         </is>
       </c>
       <c r="E94" s="15" t="n">
@@ -7434,7 +7444,7 @@
       </c>
       <c r="F94" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G94" s="15" t="inlineStr">
@@ -7444,34 +7454,34 @@
       </c>
       <c r="H94" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I94" s="15" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>24/02/2025</t>
         </is>
       </c>
       <c r="J94" s="15" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K94" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L94" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28019</t>
+          <t>PDMDEP-27535</t>
         </is>
       </c>
       <c r="M94" s="15" t="inlineStr">
         <is>
-          <t>455151</t>
+          <t>465345</t>
         </is>
       </c>
       <c r="N94" s="16" t="n">
-        <v>240</v>
-      </c>
-      <c r="O94" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P94" s="16" t="n">
@@ -7481,12 +7491,12 @@
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
@@ -7496,7 +7506,7 @@
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E95" s="12" t="n">
@@ -7509,35 +7519,27 @@
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H95" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I95" s="12" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J95" s="12" t="n">
         <v>19</v>
       </c>
       <c r="K95" s="12" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="L95" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-34362</t>
-        </is>
-      </c>
-      <c r="M95" s="12" t="inlineStr">
-        <is>
-          <t>458057</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L95" s="12" t="inlineStr"/>
+      <c r="M95" s="12" t="inlineStr"/>
       <c r="N95" s="13" t="n">
         <v>0</v>
       </c>
@@ -7551,22 +7553,22 @@
     <row r="96">
       <c r="A96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C96" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D96" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E96" s="15" t="n">
@@ -7574,7 +7576,7 @@
       </c>
       <c r="F96" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G96" s="15" t="inlineStr">
@@ -7584,34 +7586,34 @@
       </c>
       <c r="H96" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I96" s="15" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J96" s="15" t="n">
         <v>19</v>
       </c>
       <c r="K96" s="15" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="L96" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28020</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M96" s="15" t="inlineStr">
         <is>
-          <t>458057</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N96" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O96" s="16" t="n">
+        <v>240</v>
+      </c>
+      <c r="O96" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P96" s="16" t="n">
@@ -7621,22 +7623,22 @@
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-16868</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t>[Limoges] migration placier</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>Limoges</t>
+          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
         </is>
       </c>
       <c r="E97" s="12" t="n">
@@ -7644,32 +7646,40 @@
       </c>
       <c r="F97" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G97" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H97" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I97" s="12" t="inlineStr">
         <is>
-          <t>26/09/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J97" s="12" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K97" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L97" s="12" t="inlineStr"/>
-      <c r="M97" s="12" t="inlineStr"/>
+        <v>0.12</v>
+      </c>
+      <c r="L97" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-34362</t>
+        </is>
+      </c>
+      <c r="M97" s="12" t="inlineStr">
+        <is>
+          <t>458057</t>
+        </is>
+      </c>
       <c r="N97" s="13" t="n">
         <v>0</v>
       </c>
@@ -7683,12 +7693,12 @@
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14551</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t>[Perpignan] Interface formulaire</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C98" s="15" t="inlineStr">
@@ -7698,7 +7708,7 @@
       </c>
       <c r="D98" s="15" t="inlineStr">
         <is>
-          <t>[Perpignan]</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
         </is>
       </c>
       <c r="E98" s="15" t="n">
@@ -7711,7 +7721,7 @@
       </c>
       <c r="G98" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H98" s="15" t="inlineStr">
@@ -7721,17 +7731,25 @@
       </c>
       <c r="I98" s="15" t="inlineStr">
         <is>
-          <t>14/03/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J98" s="15" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="K98" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L98" s="15" t="inlineStr"/>
-      <c r="M98" s="15" t="inlineStr"/>
+        <v>0.12</v>
+      </c>
+      <c r="L98" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28020</t>
+        </is>
+      </c>
+      <c r="M98" s="15" t="inlineStr">
+        <is>
+          <t>458057</t>
+        </is>
+      </c>
       <c r="N98" s="16" t="n">
         <v>0</v>
       </c>
@@ -7745,22 +7763,22 @@
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-16868</t>
         </is>
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[Limoges] migration placier</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>Limoges</t>
         </is>
       </c>
       <c r="E99" s="12" t="n">
@@ -7768,40 +7786,32 @@
       </c>
       <c r="F99" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H99" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I99" s="12" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>26/09/2024</t>
         </is>
       </c>
       <c r="J99" s="12" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="K99" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L99" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M99" s="12" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="L99" s="12" t="inlineStr"/>
+      <c r="M99" s="12" t="inlineStr"/>
       <c r="N99" s="13" t="n">
         <v>0</v>
       </c>
@@ -7815,12 +7825,12 @@
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12241</t>
+          <t>PDMDEP-14551</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
         <is>
-          <t>[SM Routes de Guadeloupe] LITTERALIS EXPERT</t>
+          <t>[Perpignan] Interface formulaire</t>
         </is>
       </c>
       <c r="C100" s="15" t="inlineStr">
@@ -7830,13 +7840,11 @@
       </c>
       <c r="D100" s="15" t="inlineStr">
         <is>
-          <t>[SM Routes de Guadeloupe]</t>
-        </is>
-      </c>
-      <c r="E100" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement de Littéralis Expert</t>
-        </is>
+          <t>[Perpignan]</t>
+        </is>
+      </c>
+      <c r="E100" s="15" t="n">
+        <v/>
       </c>
       <c r="F100" s="15" t="inlineStr">
         <is>
@@ -7850,16 +7858,16 @@
       </c>
       <c r="H100" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I100" s="15" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>14/03/2024</t>
         </is>
       </c>
       <c r="J100" s="15" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="K100" s="15" t="n">
         <v>0.5</v>
@@ -7879,28 +7887,26 @@
     <row r="101">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-14095</t>
         </is>
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[CC PAYS SABOLIEN] Littéralis Prime hebergé CC &amp; multivilles</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E101" s="12" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t>CC du Pays Sabolien</t>
+        </is>
+      </c>
+      <c r="E101" s="12" t="n">
+        <v/>
       </c>
       <c r="F101" s="12" t="inlineStr">
         <is>
@@ -7914,19 +7920,19 @@
       </c>
       <c r="H101" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I101" s="12" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>31/01/2024</t>
         </is>
       </c>
       <c r="J101" s="12" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K101" s="12" t="n">
-        <v>3.5</v>
+        <v>0.75</v>
       </c>
       <c r="L101" s="12" t="inlineStr"/>
       <c r="M101" s="12" t="inlineStr"/>
@@ -7943,24 +7949,26 @@
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B102" s="15" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C102" s="15" t="inlineStr"/>
+          <t>[FOUGERES] ARPEGE</t>
+        </is>
+      </c>
+      <c r="C102" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D102" s="15" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E102" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>FOUGERES</t>
+        </is>
+      </c>
+      <c r="E102" s="15" t="n">
+        <v/>
       </c>
       <c r="F102" s="15" t="inlineStr">
         <is>
@@ -7969,27 +7977,35 @@
       </c>
       <c r="G102" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H102" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I102" s="15" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J102" s="15" t="n">
         <v>34</v>
       </c>
       <c r="K102" s="15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L102" s="15" t="inlineStr"/>
-      <c r="M102" s="15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L102" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M102" s="15" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N102" s="16" t="n">
         <v>0</v>
       </c>
@@ -8003,21 +8019,29 @@
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PDMDEP-12241</t>
         </is>
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
-        </is>
-      </c>
-      <c r="C103" s="12" t="inlineStr"/>
+          <t>[SM Routes de Guadeloupe] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C103" s="12" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
-        </is>
-      </c>
-      <c r="E103" s="12" t="inlineStr"/>
+          <t>[SM Routes de Guadeloupe]</t>
+        </is>
+      </c>
+      <c r="E103" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement de Littéralis Expert</t>
+        </is>
+      </c>
       <c r="F103" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -8025,35 +8049,31 @@
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H103" s="12" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H103" s="12" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I103" s="12" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J103" s="12" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="K103" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L103" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M103" s="12" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L103" s="12" t="inlineStr"/>
+      <c r="M103" s="12" t="inlineStr"/>
       <c r="N103" s="13" t="n">
-        <v>510.6</v>
-      </c>
-      <c r="O103" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P103" s="13" t="n">
@@ -8063,89 +8083,273 @@
     <row r="104">
       <c r="A104" s="14" t="inlineStr">
         <is>
+          <t>PDMDEP-12222</t>
+        </is>
+      </c>
+      <c r="B104" s="15" t="inlineStr">
+        <is>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C104" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D104" s="15" t="inlineStr">
+        <is>
+          <t>CD14</t>
+        </is>
+      </c>
+      <c r="E104" s="15" t="inlineStr">
+        <is>
+          <t>Modélisation spécifique</t>
+        </is>
+      </c>
+      <c r="F104" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G104" s="15" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H104" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I104" s="15" t="inlineStr">
+        <is>
+          <t>04/09/2023</t>
+        </is>
+      </c>
+      <c r="J104" s="15" t="n">
+        <v>34</v>
+      </c>
+      <c r="K104" s="15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L104" s="15" t="inlineStr"/>
+      <c r="M104" s="15" t="inlineStr"/>
+      <c r="N104" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-11477</t>
+        </is>
+      </c>
+      <c r="B105" s="12" t="inlineStr">
+        <is>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C105" s="12" t="inlineStr"/>
+      <c r="D105" s="12" t="inlineStr">
+        <is>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E105" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
+      <c r="F105" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G105" s="12" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H105" s="12" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I105" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2023</t>
+        </is>
+      </c>
+      <c r="J105" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="K105" s="12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="L105" s="12" t="inlineStr"/>
+      <c r="M105" s="12" t="inlineStr"/>
+      <c r="N105" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="14" t="inlineStr">
+        <is>
+          <t>PSC-1270</t>
+        </is>
+      </c>
+      <c r="B106" s="15" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="C106" s="15" t="inlineStr"/>
+      <c r="D106" s="15" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="E106" s="15" t="inlineStr"/>
+      <c r="F106" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G106" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H106" s="15" t="inlineStr"/>
+      <c r="I106" s="15" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="J106" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K106" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M106" s="15" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
+      <c r="N106" s="16" t="n">
+        <v>510.6</v>
+      </c>
+      <c r="O106" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="11" t="inlineStr">
+        <is>
           <t>PSC-1228</t>
         </is>
       </c>
-      <c r="B104" s="15" t="inlineStr">
+      <c r="B107" s="12" t="inlineStr">
         <is>
           <t>MAIRIE DE MERLEVENEZ</t>
         </is>
       </c>
-      <c r="C104" s="15" t="inlineStr"/>
-      <c r="D104" s="15" t="inlineStr">
+      <c r="C107" s="12" t="inlineStr"/>
+      <c r="D107" s="12" t="inlineStr">
         <is>
           <t>MAIRIE DE MERLEVENEZ</t>
         </is>
       </c>
-      <c r="E104" s="15" t="inlineStr"/>
-      <c r="F104" s="15" t="inlineStr">
+      <c r="E107" s="12" t="inlineStr"/>
+      <c r="F107" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="G104" s="15" t="inlineStr">
-        <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H104" s="15" t="inlineStr"/>
-      <c r="I104" s="15" t="inlineStr">
+      <c r="G107" s="12" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H107" s="12" t="inlineStr"/>
+      <c r="I107" s="12" t="inlineStr">
         <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="J104" s="15" t="n">
+      <c r="J107" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K104" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L104" s="15" t="inlineStr">
+      <c r="K107" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" s="12" t="inlineStr">
         <is>
           <t>PDMDEP-32829</t>
         </is>
       </c>
-      <c r="M104" s="15" t="inlineStr">
+      <c r="M107" s="12" t="inlineStr">
         <is>
           <t>00163534</t>
         </is>
       </c>
-      <c r="N104" s="16" t="n">
+      <c r="N107" s="13" t="n">
         <v>50</v>
       </c>
-      <c r="O104" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P104" s="16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="18" t="inlineStr">
+      <c r="O107" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B105" s="18" t="inlineStr"/>
-      <c r="C105" s="18" t="inlineStr"/>
-      <c r="D105" s="18" t="inlineStr"/>
-      <c r="E105" s="18" t="inlineStr"/>
-      <c r="F105" s="18" t="inlineStr"/>
-      <c r="G105" s="18" t="inlineStr"/>
-      <c r="H105" s="18" t="inlineStr"/>
-      <c r="I105" s="18" t="inlineStr"/>
-      <c r="J105" s="18" t="inlineStr"/>
-      <c r="K105" s="18" t="inlineStr"/>
-      <c r="L105" s="18" t="inlineStr"/>
-      <c r="M105" s="18" t="inlineStr"/>
-      <c r="N105" s="19" t="n">
+      <c r="B108" s="18" t="inlineStr"/>
+      <c r="C108" s="18" t="inlineStr"/>
+      <c r="D108" s="18" t="inlineStr"/>
+      <c r="E108" s="18" t="inlineStr"/>
+      <c r="F108" s="18" t="inlineStr"/>
+      <c r="G108" s="18" t="inlineStr"/>
+      <c r="H108" s="18" t="inlineStr"/>
+      <c r="I108" s="18" t="inlineStr"/>
+      <c r="J108" s="18" t="inlineStr"/>
+      <c r="K108" s="18" t="inlineStr"/>
+      <c r="L108" s="18" t="inlineStr"/>
+      <c r="M108" s="18" t="inlineStr"/>
+      <c r="N108" s="19" t="n">
         <v>57120.64</v>
       </c>
-      <c r="O105" s="19" t="n">
-        <v>2326.5</v>
-      </c>
-      <c r="P105" s="19" t="n">
-        <v>54.78</v>
+      <c r="O108" s="19" t="n">
+        <v>2446.5</v>
+      </c>
+      <c r="P108" s="19" t="n">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -8251,6 +8455,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId99"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId103"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8825,26 +9032,26 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>25.25</v>
+        <v>29</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>6.25</v>
+        <v>7.5</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>0.75</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>32.25</v>
+        <v>37.25</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>486.15</v>
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>7.7%</t>
         </is>
       </c>
     </row>
@@ -8858,13 +9065,13 @@
         <v>8.25</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="D6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>10.25</v>
+        <v>10.75</v>
       </c>
       <c r="F6" s="12" t="n">
         <v>2</v>
@@ -8874,7 +9081,7 @@
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>4.1%</t>
         </is>
       </c>
     </row>
@@ -8886,7 +9093,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>10.75</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -8971,10 +9178,10 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>394231</v>
+        <v>394111</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>192032</v>
+        <v>191912</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>202200</v>
@@ -8996,10 +9203,10 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>186863</v>
+        <v>186743</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>81917</v>
+        <v>81797</v>
       </c>
       <c r="D6" s="26" t="n">
         <v>104945</v>
@@ -9290,12 +9497,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
@@ -9311,7 +9518,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>1 clôture(s) : 1 projet(s), 0 rework</t>
+          <t>2 clôture(s) : 2 projet(s), 0 rework</t>
         </is>
       </c>
     </row>
@@ -9351,59 +9558,89 @@
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
         <is>
+          <t>PDMDEP-31947</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
           <t>PDMDEP-33720</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>[COMMUNE DE LEVALLOIS PERRET] - PRESTA PURGE DES ACTES EN UR</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
-        <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="F5" s="15" t="n">
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>TOTAL projets clôturés</t>
         </is>
       </c>
-      <c r="B7" s="18" t="n"/>
-      <c r="C7" s="18" t="n"/>
-      <c r="D7" s="18" t="n"/>
-      <c r="E7" s="18" t="n"/>
-      <c r="F7" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="28" t="inlineStr">
+      <c r="B8" s="18" t="n"/>
+      <c r="C8" s="18" t="n"/>
+      <c r="D8" s="18" t="n"/>
+      <c r="E8" s="18" t="n"/>
+      <c r="F8" s="18" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="28" t="inlineStr">
         <is>
           <t>TOTAL rework clôturés</t>
         </is>
       </c>
-      <c r="B8" s="28" t="n"/>
-      <c r="C8" s="28" t="n"/>
-      <c r="D8" s="28" t="n"/>
-      <c r="E8" s="28" t="n"/>
-      <c r="F8" s="28" t="n">
+      <c r="B9" s="28" t="n"/>
+      <c r="C9" s="28" t="n"/>
+      <c r="D9" s="28" t="n"/>
+      <c r="E9" s="28" t="n"/>
+      <c r="F9" s="28" t="n">
         <v>0</v>
       </c>
     </row>
